--- a/2 Output/Phase1_Baseline_Selected100_Observed/tables/phase1_baseline_origin_comparison.xlsx
+++ b/2 Output/Phase1_Baseline_Selected100_Observed/tables/phase1_baseline_origin_comparison.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="855" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="811" uniqueCount="208">
   <si>
     <t>Advancing Justice Uganda - Phase 1 baseline origin comparison</t>
   </si>
@@ -58,7 +58,7 @@
     <t>Use as implementation diagnostics in the Phase 1 Final Baseline Report.</t>
   </si>
   <si>
-    <t>Selected-list LC (interviewed)</t>
+    <t>Selected-list (observed)</t>
   </si>
   <si>
     <t>Previously contacted</t>
@@ -160,10 +160,16 @@
     <t>m6_q12_2</t>
   </si>
   <si>
+    <t>m6_q04_2</t>
+  </si>
+  <si>
     <t>idx_referral_practice</t>
   </si>
   <si>
-    <t>m6_q04_2</t>
+    <t>verified_ref_dest_score</t>
+  </si>
+  <si>
+    <t>m6_q04_3</t>
   </si>
   <si>
     <t>referral_explain_conf_score</t>
@@ -172,18 +178,12 @@
     <t>prior_formal_coordination</t>
   </si>
   <si>
-    <t>m6_q04_3</t>
-  </si>
-  <si>
-    <t>verified_ref_dest_score</t>
+    <t>verified_referral_record_score</t>
   </si>
   <si>
     <t>m6_q04_4</t>
   </si>
   <si>
-    <t>verified_referral_record_score</t>
-  </si>
-  <si>
     <t>referral_path_conf_score</t>
   </si>
   <si>
@@ -193,12 +193,12 @@
     <t>police_coordination_score</t>
   </si>
   <si>
+    <t>m6_q12_1</t>
+  </si>
+  <si>
     <t>referral_frequency_score</t>
   </si>
   <si>
-    <t>m6_q12_1</t>
-  </si>
-  <si>
     <t>comm_accepts_ex_prisoner</t>
   </si>
   <si>
@@ -292,12 +292,12 @@
     <t>lcc_women_share</t>
   </si>
   <si>
+    <t>any_serious_or_sensitive_case_3m</t>
+  </si>
+  <si>
     <t>any_child_or_sgbv_case_3m</t>
   </si>
   <si>
-    <t>any_serious_or_sensitive_case_3m</t>
-  </si>
-  <si>
     <t>can_record_runyankore</t>
   </si>
   <si>
@@ -391,10 +391,16 @@
     <t>Referral barrier: transport cost/lack of transport</t>
   </si>
   <si>
+    <t>Referral reason: serious violence/threat to life</t>
+  </si>
+  <si>
     <t>Referral practice</t>
   </si>
   <si>
-    <t>Referral reason: serious violence/threat to life</t>
+    <t>Enumerator-verified referral destination is recorded, 0-1</t>
+  </si>
+  <si>
+    <t>Referral reason: sexual violence or SGBV</t>
   </si>
   <si>
     <t>Confidence explaining referrals to community members</t>
@@ -403,33 +409,27 @@
     <t>Prior coordination with police/courts/probation/child protection/justice actors</t>
   </si>
   <si>
-    <t>Referral reason: sexual violence or SGBV</t>
-  </si>
-  <si>
-    <t>Enumerator-verified referral destination is recorded, 0-1</t>
+    <t>Enumerator-verified referred cases are recorded, 0-1</t>
   </si>
   <si>
     <t>Referral reason: child protection concern</t>
   </si>
   <si>
-    <t>Enumerator-verified referred cases are recorded, 0-1</t>
-  </si>
-  <si>
     <t>Confidence knowing where to refer cases</t>
   </si>
   <si>
-    <t>Coordination score with court/formal justice actors</t>
-  </si>
-  <si>
-    <t>Coordination score with police</t>
+    <t>Perceived ease of coordinating with court/formal justice actors</t>
+  </si>
+  <si>
+    <t>Perceived ease of coordinating with police</t>
+  </si>
+  <si>
+    <t>Referral barrier: authority too far away</t>
   </si>
   <si>
     <t>Referral practice score: frequency/regularity</t>
   </si>
   <si>
-    <t>Referral barrier: authority too far away</t>
-  </si>
-  <si>
     <t>Respondent says community members are usually willing to accept them</t>
   </si>
   <si>
@@ -523,12 +523,12 @@
     <t>Share of current LCC/LC committee members who are women</t>
   </si>
   <si>
+    <t>Reported child-related or SGBV case in past 3 months</t>
+  </si>
+  <si>
     <t>LCC received child-related or SGBV case in past 3 months</t>
   </si>
   <si>
-    <t>Any child, SGBV, or other serious/sensitive case in past 3 months</t>
-  </si>
-  <si>
     <t>Can complete LCC records in Runyankore/Runyakitara</t>
   </si>
   <si>
@@ -547,7 +547,7 @@
     <t>Enumerator-rated overall record usability score, 0-1</t>
   </si>
   <si>
-    <t>SGBV vignette: correct documentation/procedure</t>
+    <t>SGBV vignette: appropriate actor involvement/notification</t>
   </si>
   <si>
     <t>Record quality</t>
@@ -577,7 +577,7 @@
     <t>Respondent says vulnerable/sensitive cases require special handling</t>
   </si>
   <si>
-    <t>Child-related vignette: correct documentation/procedure</t>
+    <t>Child-related vignette: appropriate actor involvement/notification</t>
   </si>
   <si>
     <t>Record challenge: no pens/basic stationery</t>
@@ -644,6 +644,9 @@
   </si>
   <si>
     <t>Cross-sectional baseline associations; not causal estimates.</t>
+  </si>
+  <si>
+    <t>df_residual</t>
   </si>
 </sst>
 </file>
@@ -777,19 +780,19 @@
         <v>11</v>
       </c>
       <c r="C2" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D2" s="1">
-        <v>0.29670330882072449</v>
+        <v>0.29032257199287415</v>
       </c>
       <c r="E2" s="1">
-        <v>0.25274726748466492</v>
+        <v>0.25806450843811035</v>
       </c>
       <c r="F2" s="1">
-        <v>0.076923079788684845</v>
+        <v>0.086021505296230316</v>
       </c>
       <c r="G2" s="1">
-        <v>0.087912090122699738</v>
+        <v>0.096774190664291382</v>
       </c>
     </row>
     <row r="3">
@@ -821,7 +824,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -861,6 +864,9 @@
       <c r="L1" t="s">
         <v>205</v>
       </c>
+      <c r="M1" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
@@ -870,34 +876,37 @@
         <v>110</v>
       </c>
       <c r="C2" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D2" s="1">
-        <v>0.67648417707327957</v>
+        <v>0.67828619063541451</v>
       </c>
       <c r="E2" s="1">
         <v>0.80842424793676892</v>
       </c>
       <c r="F2" s="1">
-        <v>0.13194006681442261</v>
+        <v>0.13013805449008942</v>
       </c>
       <c r="G2" s="1">
-        <v>0.13352385248784779</v>
+        <v>0.13075901602885559</v>
       </c>
       <c r="H2" s="1">
-        <v>0.023501584578491601</v>
+        <v>0.023335991400102701</v>
       </c>
       <c r="I2" s="1">
-        <v>0.086944475769996643</v>
+        <v>0.084517188370227814</v>
       </c>
       <c r="J2" s="1">
-        <v>0.18010322749614716</v>
+        <v>0.17700083553791046</v>
       </c>
       <c r="K2" s="1">
-        <v>1.12443364887e-07</v>
+        <v>1.5489128481199999e-07</v>
       </c>
       <c r="L2" t="s">
         <v>206</v>
+      </c>
+      <c r="M2" s="1">
+        <v>111</v>
       </c>
     </row>
     <row r="3">
@@ -908,34 +917,37 @@
         <v>112</v>
       </c>
       <c r="C3" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D3" s="1">
-        <v>0.66870664927985646</v>
+        <v>0.66913728143579221</v>
       </c>
       <c r="E3" s="1">
         <v>0.74123304946856061</v>
       </c>
       <c r="F3" s="1">
-        <v>0.072526402771472931</v>
+        <v>0.072095766663551331</v>
       </c>
       <c r="G3" s="1">
-        <v>0.072686603949093695</v>
+        <v>0.072390912772540506</v>
       </c>
       <c r="H3" s="1">
-        <v>0.032381982855789103</v>
+        <v>0.032435450336743603</v>
       </c>
       <c r="I3" s="1">
-        <v>0.0085065662860870361</v>
+        <v>0.0081179030239582062</v>
       </c>
       <c r="J3" s="1">
-        <v>0.13686664402484894</v>
+        <v>0.13666392862796784</v>
       </c>
       <c r="K3" s="1">
-        <v>0.026809045293572899</v>
+        <v>0.027633536797177099</v>
       </c>
       <c r="L3" t="s">
         <v>206</v>
+      </c>
+      <c r="M3" s="1">
+        <v>111</v>
       </c>
     </row>
     <row r="4">
@@ -946,34 +958,37 @@
         <v>27</v>
       </c>
       <c r="C4" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D4" s="1">
-        <v>0.61083811914527808</v>
+        <v>0.61174751417611239</v>
       </c>
       <c r="E4" s="1">
         <v>0.6348355656320398</v>
       </c>
       <c r="F4" s="1">
-        <v>0.023997446522116661</v>
+        <v>0.023088051006197929</v>
       </c>
       <c r="G4" s="1">
-        <v>0.025643211987156099</v>
+        <v>0.023925287751462999</v>
       </c>
       <c r="H4" s="1">
-        <v>0.024697826990098402</v>
+        <v>0.024653485998332999</v>
       </c>
       <c r="I4" s="1">
-        <v>-0.023307077586650848</v>
+        <v>-0.024927239865064621</v>
       </c>
       <c r="J4" s="1">
-        <v>0.074593499302864075</v>
+        <v>0.072777815163135529</v>
       </c>
       <c r="K4" s="1">
-        <v>0.30143838244592208</v>
+        <v>0.33392586668415231</v>
       </c>
       <c r="L4" t="s">
         <v>206</v>
+      </c>
+      <c r="M4" s="1">
+        <v>111</v>
       </c>
     </row>
     <row r="5">
@@ -984,34 +999,37 @@
         <v>111</v>
       </c>
       <c r="C5" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D5" s="1">
-        <v>0.6410022639966273</v>
+        <v>0.64271773253717734</v>
       </c>
       <c r="E5" s="1">
         <v>0.71757883917201648</v>
       </c>
       <c r="F5" s="1">
-        <v>0.076576575636863708</v>
+        <v>0.074861109256744385</v>
       </c>
       <c r="G5" s="1">
-        <v>0.077763251642035305</v>
+        <v>0.075351792348510097</v>
       </c>
       <c r="H5" s="1">
-        <v>0.019689713480136501</v>
+        <v>0.019670301982851499</v>
       </c>
       <c r="I5" s="1">
-        <v>0.038738880306482315</v>
+        <v>0.036373775452375412</v>
       </c>
       <c r="J5" s="1">
-        <v>0.1167876273393631</v>
+        <v>0.11432980746030807</v>
       </c>
       <c r="K5" s="1">
-        <v>0.000139252480855</v>
+        <v>0.0002120617825066</v>
       </c>
       <c r="L5" t="s">
         <v>206</v>
+      </c>
+      <c r="M5" s="1">
+        <v>111</v>
       </c>
     </row>
     <row r="6">
@@ -1022,72 +1040,78 @@
         <v>175</v>
       </c>
       <c r="C6" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D6" s="1">
-        <v>0.52304385131695763</v>
+        <v>0.52456441365422746</v>
       </c>
       <c r="E6" s="1">
         <v>0.71448863636363635</v>
       </c>
       <c r="F6" s="1">
-        <v>0.19144478440284729</v>
+        <v>0.18992422521114349</v>
       </c>
       <c r="G6" s="1">
-        <v>0.19408548999843289</v>
+        <v>0.19133539962063531</v>
       </c>
       <c r="H6" s="1">
-        <v>0.048675094284900897</v>
+        <v>0.048178752283829701</v>
       </c>
       <c r="I6" s="1">
-        <v>0.097613036632537842</v>
+        <v>0.095865987241268158</v>
       </c>
       <c r="J6" s="1">
-        <v>0.29055795073509216</v>
+        <v>0.28680482506752014</v>
       </c>
       <c r="K6" s="1">
-        <v>0.0001211881374594</v>
+        <v>0.0001272769286991</v>
       </c>
       <c r="L6" t="s">
         <v>206</v>
       </c>
+      <c r="M6" s="1">
+        <v>111</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C7" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D7" s="1">
-        <v>0.61510880062213313</v>
+        <v>0.615209507205153</v>
       </c>
       <c r="E7" s="1">
         <v>0.69829996065659961</v>
       </c>
       <c r="F7" s="1">
-        <v>0.083191156387329102</v>
+        <v>0.083090454339981079</v>
       </c>
       <c r="G7" s="1">
-        <v>0.086382323565427896</v>
+        <v>0.085053223485317797</v>
       </c>
       <c r="H7" s="1">
-        <v>0.0374182898066431</v>
+        <v>0.037207968855664603</v>
       </c>
       <c r="I7" s="1">
-        <v>0.012220489792525768</v>
+        <v>0.011323149316012859</v>
       </c>
       <c r="J7" s="1">
-        <v>0.16054415702819824</v>
+        <v>0.15878330171108246</v>
       </c>
       <c r="K7" s="1">
-        <v>0.022854454520505899</v>
+        <v>0.0241592955839613</v>
       </c>
       <c r="L7" t="s">
         <v>206</v>
+      </c>
+      <c r="M7" s="1">
+        <v>111</v>
       </c>
     </row>
     <row r="8">
@@ -1098,34 +1122,37 @@
         <v>181</v>
       </c>
       <c r="C8" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D8" s="1">
-        <v>0.69803114464649785</v>
+        <v>0.69959678268560799</v>
       </c>
       <c r="E8" s="1">
         <v>0.75931188193234533</v>
       </c>
       <c r="F8" s="1">
-        <v>0.061280738562345505</v>
+        <v>0.059715099632740021</v>
       </c>
       <c r="G8" s="1">
-        <v>0.050959189019124398</v>
+        <v>0.050797553231641999</v>
       </c>
       <c r="H8" s="1">
-        <v>0.050795663262046799</v>
+        <v>0.0507967899631682</v>
       </c>
       <c r="I8" s="1">
-        <v>-0.04971616342663765</v>
+        <v>-0.049859676510095596</v>
       </c>
       <c r="J8" s="1">
-        <v>0.15163454413414001</v>
+        <v>0.15145477652549744</v>
       </c>
       <c r="K8" s="1">
-        <v>0.31797699314107508</v>
+        <v>0.31947826824520409</v>
       </c>
       <c r="L8" t="s">
         <v>206</v>
+      </c>
+      <c r="M8" s="1">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -1162,13 +1189,13 @@
         <v>11</v>
       </c>
       <c r="C2" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D2" s="1">
-        <v>0.8053097128868103</v>
+        <v>0.80869567394256592</v>
       </c>
       <c r="E2" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3">
@@ -1182,10 +1209,10 @@
         <v>22</v>
       </c>
       <c r="D3" s="1">
-        <v>0.1946902722120285</v>
+        <v>0.19130434095859528</v>
       </c>
       <c r="E3" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -1228,13 +1255,13 @@
         <v>11</v>
       </c>
       <c r="D2" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E2" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F2" s="1">
-        <v>0.85106384754180908</v>
+        <v>0.85416668653488159</v>
       </c>
     </row>
     <row r="3">
@@ -1251,10 +1278,10 @@
         <v>7</v>
       </c>
       <c r="E3" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F3" s="1">
-        <v>0.14893616735935211</v>
+        <v>0.1458333283662796</v>
       </c>
     </row>
     <row r="4">
@@ -1308,13 +1335,13 @@
         <v>11</v>
       </c>
       <c r="D6" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6" s="1">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" s="1">
-        <v>0.71875</v>
+        <v>0.72727274894714355</v>
       </c>
     </row>
     <row r="7">
@@ -1331,10 +1358,10 @@
         <v>9</v>
       </c>
       <c r="E7" s="1">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F7" s="1">
-        <v>0.28125</v>
+        <v>0.27272728085517883</v>
       </c>
     </row>
   </sheetData>
@@ -1343,7 +1370,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J83"/>
+  <dimension ref="A1:J78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1389,10 +1416,10 @@
         <v>110</v>
       </c>
       <c r="D2" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E2" s="1">
-        <v>0.67648417707327957</v>
+        <v>0.67828619063541451</v>
       </c>
       <c r="F2" s="1">
         <v>22</v>
@@ -1401,13 +1428,13 @@
         <v>0.80842424793676892</v>
       </c>
       <c r="H2" s="1">
-        <v>0.13194007086348941</v>
+        <v>0.13013805730135439</v>
       </c>
       <c r="I2" s="1">
-        <v>1.51330004656e-05</v>
+        <v>1.9104368201999999e-05</v>
       </c>
       <c r="J2" s="1">
-        <v>0.13194007086348941</v>
+        <v>0.13013805730135439</v>
       </c>
     </row>
     <row r="3">
@@ -1421,10 +1448,10 @@
         <v>111</v>
       </c>
       <c r="D3" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E3" s="1">
-        <v>0.6410022639966273</v>
+        <v>0.64271773253717734</v>
       </c>
       <c r="F3" s="1">
         <v>22</v>
@@ -1433,13 +1460,13 @@
         <v>0.71757883917201648</v>
       </c>
       <c r="H3" s="1">
-        <v>0.076576575175389197</v>
+        <v>0.074861106634839095</v>
       </c>
       <c r="I3" s="1">
-        <v>0.00037670378643190001</v>
+        <v>0.00054342656699579999</v>
       </c>
       <c r="J3" s="1">
-        <v>0.076576575175389197</v>
+        <v>0.074861106634839095</v>
       </c>
     </row>
     <row r="4">
@@ -1453,10 +1480,10 @@
         <v>112</v>
       </c>
       <c r="D4" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E4" s="1">
-        <v>0.66870664927985646</v>
+        <v>0.66913728143579221</v>
       </c>
       <c r="F4" s="1">
         <v>22</v>
@@ -1465,13 +1492,13 @@
         <v>0.74123304946856061</v>
       </c>
       <c r="H4" s="1">
-        <v>0.072526400188704196</v>
+        <v>0.072095768032768404</v>
       </c>
       <c r="I4" s="1">
-        <v>0.015245241111370799</v>
+        <v>0.015769077113338699</v>
       </c>
       <c r="J4" s="1">
-        <v>0.072526400188704196</v>
+        <v>0.072095768032768404</v>
       </c>
     </row>
     <row r="5">
@@ -1485,10 +1512,10 @@
         <v>27</v>
       </c>
       <c r="D5" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E5" s="1">
-        <v>0.61083811914527808</v>
+        <v>0.61174751417611239</v>
       </c>
       <c r="F5" s="1">
         <v>22</v>
@@ -1497,13 +1524,13 @@
         <v>0.6348355656320398</v>
       </c>
       <c r="H5" s="1">
-        <v>0.023997446486761699</v>
+        <v>0.023088051455927398</v>
       </c>
       <c r="I5" s="1">
-        <v>0.37017392314130881</v>
+        <v>0.39299283822349318</v>
       </c>
       <c r="J5" s="1">
-        <v>0.023997446486761699</v>
+        <v>0.023088051455927398</v>
       </c>
     </row>
     <row r="6">
@@ -1517,10 +1544,10 @@
         <v>113</v>
       </c>
       <c r="D6" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E6" s="1">
-        <v>0.76128336263226937</v>
+        <v>0.76238479569394102</v>
       </c>
       <c r="F6" s="1">
         <v>22</v>
@@ -1529,13 +1556,13 @@
         <v>0.89157197421247314</v>
       </c>
       <c r="H6" s="1">
-        <v>0.1302886115802038</v>
+        <v>0.12918717851853209</v>
       </c>
       <c r="I6" s="1">
-        <v>0.00020955452112240001</v>
+        <v>0.00024086750106500001</v>
       </c>
       <c r="J6" s="1">
-        <v>0.1302886115802038</v>
+        <v>0.12918717851853209</v>
       </c>
     </row>
     <row r="7">
@@ -1549,10 +1576,10 @@
         <v>114</v>
       </c>
       <c r="D7" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E7" s="1">
-        <v>0.65477272647095253</v>
+        <v>0.65486559055505256</v>
       </c>
       <c r="F7" s="1">
         <v>22</v>
@@ -1561,13 +1588,13 @@
         <v>0.75867769257588824</v>
       </c>
       <c r="H7" s="1">
-        <v>0.1039049661049357</v>
+        <v>0.1038121020208357</v>
       </c>
       <c r="I7" s="1">
-        <v>0.023254832145028301</v>
+        <v>0.022014726228919299</v>
       </c>
       <c r="J7" s="1">
-        <v>0.1039049661049357</v>
+        <v>0.1038121020208357</v>
       </c>
     </row>
     <row r="8">
@@ -1581,10 +1608,10 @@
         <v>115</v>
       </c>
       <c r="D8" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E8" s="1">
-        <v>0.60798011621931092</v>
+        <v>0.61169994950935402</v>
       </c>
       <c r="F8" s="1">
         <v>22</v>
@@ -1593,13 +1620,13 @@
         <v>0.68582250719720672</v>
       </c>
       <c r="H8" s="1">
-        <v>0.077842390977895804</v>
+        <v>0.074122557687852697</v>
       </c>
       <c r="I8" s="1">
-        <v>0.022874150237429801</v>
+        <v>0.029959187331934801</v>
       </c>
       <c r="J8" s="1">
-        <v>0.077842390977895804</v>
+        <v>0.074122557687852697</v>
       </c>
     </row>
     <row r="9">
@@ -1613,10 +1640,10 @@
         <v>116</v>
       </c>
       <c r="D9" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E9" s="1">
-        <v>0.74512531829404305</v>
+        <v>0.7479093616367668</v>
       </c>
       <c r="F9" s="1">
         <v>22</v>
@@ -1625,13 +1652,13 @@
         <v>0.81921211697838525</v>
       </c>
       <c r="H9" s="1">
-        <v>0.074086798684342203</v>
+        <v>0.071302755341618507</v>
       </c>
       <c r="I9" s="1">
-        <v>0.0142565558822026</v>
+        <v>0.019539672517746899</v>
       </c>
       <c r="J9" s="1">
-        <v>0.074086798684342203</v>
+        <v>0.071302755341618507</v>
       </c>
     </row>
     <row r="10">
@@ -1645,10 +1672,10 @@
         <v>117</v>
       </c>
       <c r="D10" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E10" s="1">
-        <v>0.70691392185923818</v>
+        <v>0.70687724249337314</v>
       </c>
       <c r="F10" s="1">
         <v>22</v>
@@ -1657,13 +1684,13 @@
         <v>0.7486426803198728</v>
       </c>
       <c r="H10" s="1">
-        <v>0.041728758460634598</v>
+        <v>0.041765437826499698</v>
       </c>
       <c r="I10" s="1">
-        <v>0.19143151962259569</v>
+        <v>0.19719782960896681</v>
       </c>
       <c r="J10" s="1">
-        <v>0.041728758460634598</v>
+        <v>0.041765437826499698</v>
       </c>
     </row>
     <row r="11">
@@ -1677,10 +1704,10 @@
         <v>118</v>
       </c>
       <c r="D11" s="1">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E11" s="1">
-        <v>0.45170454545454553</v>
+        <v>0.46111111111111108</v>
       </c>
       <c r="F11" s="1">
         <v>22</v>
@@ -1689,13 +1716,13 @@
         <v>0.67045454545454541</v>
       </c>
       <c r="H11" s="1">
-        <v>0.21874999999999989</v>
+        <v>0.2093434343434343</v>
       </c>
       <c r="I11" s="1">
-        <v>0.0011524680243634</v>
+        <v>0.0018960041074505001</v>
       </c>
       <c r="J11" s="1">
-        <v>0.21874999999999989</v>
+        <v>0.2093434343434343</v>
       </c>
     </row>
     <row r="12">
@@ -1709,10 +1736,10 @@
         <v>119</v>
       </c>
       <c r="D12" s="1">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E12" s="1">
-        <v>0.42897727272727271</v>
+        <v>0.42222222222222222</v>
       </c>
       <c r="F12" s="1">
         <v>21</v>
@@ -1721,13 +1748,13 @@
         <v>0.6071428571428571</v>
       </c>
       <c r="H12" s="1">
-        <v>0.17816558441558439</v>
+        <v>0.1849206349206349</v>
       </c>
       <c r="I12" s="1">
-        <v>0.011995828540544</v>
+        <v>0.0082921406870097008</v>
       </c>
       <c r="J12" s="1">
-        <v>0.17816558441558439</v>
+        <v>0.1849206349206349</v>
       </c>
     </row>
     <row r="13">
@@ -1741,10 +1768,10 @@
         <v>120</v>
       </c>
       <c r="D13" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E13" s="1">
-        <v>0.8351648351648352</v>
+        <v>0.83870967741935487</v>
       </c>
       <c r="F13" s="1">
         <v>22</v>
@@ -1753,13 +1780,13 @@
         <v>0.95454545454545459</v>
       </c>
       <c r="H13" s="1">
-        <v>0.1193806193806194</v>
+        <v>0.1158357771260997</v>
       </c>
       <c r="I13" s="1">
-        <v>0.15216897342503741</v>
+        <v>0.1607752812799218</v>
       </c>
       <c r="J13" s="1">
-        <v>0.1193806193806194</v>
+        <v>0.1158357771260997</v>
       </c>
     </row>
     <row r="14">
@@ -1773,10 +1800,10 @@
         <v>121</v>
       </c>
       <c r="D14" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E14" s="1">
-        <v>0.45054945054945062</v>
+        <v>0.43010752688172038</v>
       </c>
       <c r="F14" s="1">
         <v>22</v>
@@ -1785,13 +1812,13 @@
         <v>0.54545454545454541</v>
       </c>
       <c r="H14" s="1">
-        <v>0.0949050949050948</v>
+        <v>0.11534701857282501</v>
       </c>
       <c r="I14" s="1">
-        <v>0.4279525320297285</v>
+        <v>0.3326032191300492</v>
       </c>
       <c r="J14" s="1">
-        <v>0.0949050949050948</v>
+        <v>0.11534701857282501</v>
       </c>
     </row>
     <row r="15">
@@ -1805,25 +1832,25 @@
         <v>122</v>
       </c>
       <c r="D15" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E15" s="1">
-        <v>0.61510880062213313</v>
+        <v>0.68817204301075274</v>
       </c>
       <c r="F15" s="1">
         <v>22</v>
       </c>
       <c r="G15" s="1">
-        <v>0.69829996065659961</v>
+        <v>0.77272727272727271</v>
       </c>
       <c r="H15" s="1">
-        <v>0.083191160034466499</v>
+        <v>0.084555229716520006</v>
       </c>
       <c r="I15" s="1">
-        <v>0.025535190366513801</v>
+        <v>0.43890215547745593</v>
       </c>
       <c r="J15" s="1">
-        <v>0.083191160034466499</v>
+        <v>0.084555229716520006</v>
       </c>
     </row>
     <row r="16">
@@ -1831,16 +1858,16 @@
         <v>26</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D16" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E16" s="1">
-        <v>0.61510880062213313</v>
+        <v>0.615209507205153</v>
       </c>
       <c r="F16" s="1">
         <v>22</v>
@@ -1849,13 +1876,13 @@
         <v>0.69829996065659961</v>
       </c>
       <c r="H16" s="1">
-        <v>0.083191160034466499</v>
+        <v>0.083090453451446597</v>
       </c>
       <c r="I16" s="1">
-        <v>0.025535190366513801</v>
+        <v>0.023705043506038501</v>
       </c>
       <c r="J16" s="1">
-        <v>0.083191160034466499</v>
+        <v>0.083090453451446597</v>
       </c>
     </row>
     <row r="17">
@@ -1863,31 +1890,31 @@
         <v>26</v>
       </c>
       <c r="B17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D17" s="1">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="E17" s="1">
-        <v>0.69230769230769229</v>
+        <v>0.6875</v>
       </c>
       <c r="F17" s="1">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G17" s="1">
-        <v>0.77272727272727271</v>
+        <v>0.76470588235294113</v>
       </c>
       <c r="H17" s="1">
-        <v>0.080419580419580403</v>
+        <v>0.077205882352941096</v>
       </c>
       <c r="I17" s="1">
-        <v>0.46107928367593493</v>
+        <v>0.49698882369010422</v>
       </c>
       <c r="J17" s="1">
-        <v>0.080419580419580403</v>
+        <v>0.077205882352941096</v>
       </c>
     </row>
     <row r="18">
@@ -1895,31 +1922,31 @@
         <v>26</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C18" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D18" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E18" s="1">
-        <v>0.58241758241758246</v>
+        <v>0.4838709677419355</v>
       </c>
       <c r="F18" s="1">
         <v>22</v>
       </c>
       <c r="G18" s="1">
-        <v>0.65909090909090906</v>
+        <v>0.40909090909090912</v>
       </c>
       <c r="H18" s="1">
-        <v>0.076673326673326603</v>
+        <v>-0.074780058651026396</v>
       </c>
       <c r="I18" s="1">
-        <v>0.14808856021965239</v>
+        <v>0.53154290901188228</v>
       </c>
       <c r="J18" s="1">
-        <v>0.076673326673326603</v>
+        <v>0.074780058651026396</v>
       </c>
     </row>
     <row r="19">
@@ -1927,31 +1954,31 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C19" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D19" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E19" s="1">
-        <v>0.87912087912087911</v>
+        <v>0.58602150537634412</v>
       </c>
       <c r="F19" s="1">
         <v>22</v>
       </c>
       <c r="G19" s="1">
-        <v>0.95454545454545459</v>
+        <v>0.65909090909090906</v>
       </c>
       <c r="H19" s="1">
-        <v>0.075424575424575493</v>
+        <v>0.073069403714564898</v>
       </c>
       <c r="I19" s="1">
-        <v>0.30705810298076669</v>
+        <v>0.16534088350526069</v>
       </c>
       <c r="J19" s="1">
-        <v>0.075424575424575493</v>
+        <v>0.073069403714564898</v>
       </c>
     </row>
     <row r="20">
@@ -1959,31 +1986,31 @@
         <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D20" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E20" s="1">
-        <v>0.48351648351648352</v>
+        <v>0.88172043010752688</v>
       </c>
       <c r="F20" s="1">
         <v>22</v>
       </c>
       <c r="G20" s="1">
-        <v>0.40909090909090912</v>
+        <v>0.95454545454545459</v>
       </c>
       <c r="H20" s="1">
-        <v>-0.074425574425574403</v>
+        <v>0.072825024437927696</v>
       </c>
       <c r="I20" s="1">
-        <v>0.53440024041636403</v>
+        <v>0.31924939276812558</v>
       </c>
       <c r="J20" s="1">
-        <v>0.074425574425574403</v>
+        <v>0.072825024437927696</v>
       </c>
     </row>
     <row r="21">
@@ -1991,31 +2018,31 @@
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D21" s="1">
         <v>55</v>
       </c>
       <c r="E21" s="1">
-        <v>0.69090909090909092</v>
+        <v>0.71818181818181814</v>
       </c>
       <c r="F21" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G21" s="1">
-        <v>0.76470588235294113</v>
+        <v>0.65625</v>
       </c>
       <c r="H21" s="1">
-        <v>0.073796791443850193</v>
+        <v>-0.061931818181818102</v>
       </c>
       <c r="I21" s="1">
-        <v>0.51936252607505184</v>
+        <v>0.59880668484187516</v>
       </c>
       <c r="J21" s="1">
-        <v>0.073796791443850193</v>
+        <v>0.061931818181818102</v>
       </c>
     </row>
     <row r="22">
@@ -2023,16 +2050,16 @@
         <v>26</v>
       </c>
       <c r="B22" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C22" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D22" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E22" s="1">
-        <v>0.2087912087912088</v>
+        <v>0.21505376344086019</v>
       </c>
       <c r="F22" s="1">
         <v>22</v>
@@ -2041,13 +2068,13 @@
         <v>0.27272727272727271</v>
       </c>
       <c r="H22" s="1">
-        <v>0.063936063936063894</v>
+        <v>0.057673509286412503</v>
       </c>
       <c r="I22" s="1">
-        <v>0.52104617563932409</v>
+        <v>0.56486310795380701</v>
       </c>
       <c r="J22" s="1">
-        <v>0.063936063936063894</v>
+        <v>0.057673509286412503</v>
       </c>
     </row>
     <row r="23">
@@ -2055,31 +2082,31 @@
         <v>26</v>
       </c>
       <c r="B23" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C23" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D23" s="1">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="E23" s="1">
-        <v>0.71698113207547165</v>
+        <v>0.59408602150537637</v>
       </c>
       <c r="F23" s="1">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G23" s="1">
-        <v>0.65625</v>
+        <v>0.64772727272727271</v>
       </c>
       <c r="H23" s="1">
-        <v>-0.060731132075471601</v>
+        <v>0.053641251221896301</v>
       </c>
       <c r="I23" s="1">
-        <v>0.61077787700083586</v>
+        <v>0.28780031279951213</v>
       </c>
       <c r="J23" s="1">
-        <v>0.060731132075471601</v>
+        <v>0.053641251221896301</v>
       </c>
     </row>
     <row r="24">
@@ -2087,31 +2114,31 @@
         <v>26</v>
       </c>
       <c r="B24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C24" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D24" s="1">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E24" s="1">
-        <v>0.59340659340659341</v>
+        <v>0.702247191011236</v>
       </c>
       <c r="F24" s="1">
         <v>22</v>
       </c>
       <c r="G24" s="1">
-        <v>0.64772727272727271</v>
+        <v>0.75</v>
       </c>
       <c r="H24" s="1">
-        <v>0.054320679320679299</v>
+        <v>0.047752808988764002</v>
       </c>
       <c r="I24" s="1">
-        <v>0.28551869536860558</v>
+        <v>0.51920550288726419</v>
       </c>
       <c r="J24" s="1">
-        <v>0.054320679320679299</v>
+        <v>0.047752808988764002</v>
       </c>
     </row>
     <row r="25">
@@ -2119,31 +2146,31 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C25" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D25" s="1">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E25" s="1">
-        <v>0.69827586206896552</v>
+        <v>0.74725274725274726</v>
       </c>
       <c r="F25" s="1">
         <v>22</v>
       </c>
       <c r="G25" s="1">
-        <v>0.75</v>
+        <v>0.78409090909090906</v>
       </c>
       <c r="H25" s="1">
-        <v>0.051724137931034503</v>
+        <v>0.036838161838161798</v>
       </c>
       <c r="I25" s="1">
-        <v>0.48825865975192989</v>
+        <v>0.59172546051504582</v>
       </c>
       <c r="J25" s="1">
-        <v>0.051724137931034503</v>
+        <v>0.036838161838161798</v>
       </c>
     </row>
     <row r="26">
@@ -2151,31 +2178,31 @@
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C26" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D26" s="1">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E26" s="1">
-        <v>0.7443820224719101</v>
+        <v>0.5161290322580645</v>
       </c>
       <c r="F26" s="1">
         <v>22</v>
       </c>
       <c r="G26" s="1">
-        <v>0.78409090909090906</v>
+        <v>0.54545454545454541</v>
       </c>
       <c r="H26" s="1">
-        <v>0.039708886618998997</v>
+        <v>0.029325513196480898</v>
       </c>
       <c r="I26" s="1">
-        <v>0.56625226823520469</v>
+        <v>0.8064949829553979</v>
       </c>
       <c r="J26" s="1">
-        <v>0.039708886618998997</v>
+        <v>0.029325513196480898</v>
       </c>
     </row>
     <row r="27">
@@ -2183,16 +2210,16 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C27" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D27" s="1">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E27" s="1">
-        <v>0.76162790697674421</v>
+        <v>0.74715909090909094</v>
       </c>
       <c r="F27" s="1">
         <v>22</v>
@@ -2201,45 +2228,45 @@
         <v>0.72727272727272729</v>
       </c>
       <c r="H27" s="1">
-        <v>-0.0343551797040169</v>
+        <v>-0.019886363636363601</v>
       </c>
       <c r="I27" s="1">
-        <v>0.60952823223207053</v>
+        <v>0.77525265137558042</v>
       </c>
       <c r="J27" s="1">
-        <v>0.0343551797040169</v>
+        <v>0.019886363636363601</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C28" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D28" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E28" s="1">
-        <v>0.51648351648351654</v>
+        <v>0.30107526881720431</v>
       </c>
       <c r="F28" s="1">
         <v>22</v>
       </c>
       <c r="G28" s="1">
-        <v>0.54545454545454541</v>
+        <v>0.13636363636363641</v>
       </c>
       <c r="H28" s="1">
-        <v>0.028971028971028899</v>
+        <v>-0.1647116324535679</v>
       </c>
       <c r="I28" s="1">
-        <v>0.80921216276490049</v>
+        <v>0.11948466631400551</v>
       </c>
       <c r="J28" s="1">
-        <v>0.028971028971028899</v>
+        <v>0.1647116324535679</v>
       </c>
     </row>
     <row r="29">
@@ -2247,31 +2274,31 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C29" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D29" s="1">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E29" s="1">
-        <v>0.2967032967032967</v>
+        <v>0.5252808988764045</v>
       </c>
       <c r="F29" s="1">
         <v>22</v>
       </c>
       <c r="G29" s="1">
-        <v>0.13636363636363641</v>
+        <v>0.375</v>
       </c>
       <c r="H29" s="1">
-        <v>-0.16033966033966029</v>
+        <v>-0.1502808988764045</v>
       </c>
       <c r="I29" s="1">
-        <v>0.1287057679630938</v>
+        <v>0.038062927313723197</v>
       </c>
       <c r="J29" s="1">
-        <v>0.16033966033966029</v>
+        <v>0.1502808988764045</v>
       </c>
     </row>
     <row r="30">
@@ -2279,31 +2306,31 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C30" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D30" s="1">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E30" s="1">
-        <v>0.52011494252873558</v>
+        <v>0.59677419354838712</v>
       </c>
       <c r="F30" s="1">
         <v>22</v>
       </c>
       <c r="G30" s="1">
-        <v>0.375</v>
+        <v>0.72727272727272729</v>
       </c>
       <c r="H30" s="1">
-        <v>-0.14511494252873561</v>
+        <v>0.1304985337243402</v>
       </c>
       <c r="I30" s="1">
-        <v>0.043689650194955701</v>
+        <v>0.010965617038097701</v>
       </c>
       <c r="J30" s="1">
-        <v>0.14511494252873561</v>
+        <v>0.1304985337243402</v>
       </c>
     </row>
     <row r="31">
@@ -2311,31 +2338,31 @@
         <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C31" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D31" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E31" s="1">
-        <v>0.59615384615384615</v>
+        <v>0.59677419354838712</v>
       </c>
       <c r="F31" s="1">
         <v>22</v>
       </c>
       <c r="G31" s="1">
-        <v>0.72727272727272729</v>
+        <v>0.69318181818181823</v>
       </c>
       <c r="H31" s="1">
-        <v>0.13111888111888109</v>
+        <v>0.096407624633431097</v>
       </c>
       <c r="I31" s="1">
-        <v>0.0112288864446566</v>
+        <v>0.064734462072081403</v>
       </c>
       <c r="J31" s="1">
-        <v>0.13111888111888109</v>
+        <v>0.096407624633431097</v>
       </c>
     </row>
     <row r="32">
@@ -2343,31 +2370,31 @@
         <v>27</v>
       </c>
       <c r="B32" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C32" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D32" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E32" s="1">
-        <v>0.59340659340659341</v>
+        <v>0.086021505376344107</v>
       </c>
       <c r="F32" s="1">
         <v>22</v>
       </c>
       <c r="G32" s="1">
-        <v>0.69318181818181823</v>
+        <v>0</v>
       </c>
       <c r="H32" s="1">
-        <v>0.099775224775224797</v>
+        <v>-0.086021505376344107</v>
       </c>
       <c r="I32" s="1">
-        <v>0.057697490578584601</v>
+        <v>0.15651386444400159</v>
       </c>
       <c r="J32" s="1">
-        <v>0.099775224775224797</v>
+        <v>0.086021505376344107</v>
       </c>
     </row>
     <row r="33">
@@ -2375,31 +2402,31 @@
         <v>27</v>
       </c>
       <c r="B33" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C33" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D33" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E33" s="1">
-        <v>0.087912087912087905</v>
+        <v>0.61021505376344087</v>
       </c>
       <c r="F33" s="1">
         <v>22</v>
       </c>
       <c r="G33" s="1">
-        <v>0</v>
+        <v>0.69318181818181823</v>
       </c>
       <c r="H33" s="1">
-        <v>-0.087912087912087905</v>
+        <v>0.082966764418377401</v>
       </c>
       <c r="I33" s="1">
-        <v>0.1517681784726721</v>
+        <v>0.11299979230854509</v>
       </c>
       <c r="J33" s="1">
-        <v>0.087912087912087905</v>
+        <v>0.082966764418377401</v>
       </c>
     </row>
     <row r="34">
@@ -2407,31 +2434,31 @@
         <v>27</v>
       </c>
       <c r="B34" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C34" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D34" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E34" s="1">
-        <v>0.61263736263736268</v>
+        <v>0.59946236559139787</v>
       </c>
       <c r="F34" s="1">
         <v>22</v>
       </c>
       <c r="G34" s="1">
-        <v>0.69318181818181823</v>
+        <v>0.68181818181818177</v>
       </c>
       <c r="H34" s="1">
-        <v>0.080544455544455607</v>
+        <v>0.082355816226783896</v>
       </c>
       <c r="I34" s="1">
-        <v>0.12273202904129769</v>
+        <v>0.081563711558646695</v>
       </c>
       <c r="J34" s="1">
-        <v>0.080544455544455607</v>
+        <v>0.082355816226783896</v>
       </c>
     </row>
     <row r="35">
@@ -2439,31 +2466,31 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C35" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D35" s="1">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E35" s="1">
-        <v>0.60164835164835162</v>
+        <v>0.6713483146067416</v>
       </c>
       <c r="F35" s="1">
         <v>22</v>
       </c>
       <c r="G35" s="1">
-        <v>0.68181818181818177</v>
+        <v>0.75</v>
       </c>
       <c r="H35" s="1">
-        <v>0.080169830169830106</v>
+        <v>0.078651685393258397</v>
       </c>
       <c r="I35" s="1">
-        <v>0.088129803214070601</v>
+        <v>0.17307573740344351</v>
       </c>
       <c r="J35" s="1">
-        <v>0.080169830169830106</v>
+        <v>0.078651685393258397</v>
       </c>
     </row>
     <row r="36">
@@ -2471,31 +2498,31 @@
         <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C36" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D36" s="1">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E36" s="1">
-        <v>0.67241379310344829</v>
+        <v>0.59139784946236562</v>
       </c>
       <c r="F36" s="1">
         <v>22</v>
       </c>
       <c r="G36" s="1">
-        <v>0.75</v>
+        <v>0.65909090909090906</v>
       </c>
       <c r="H36" s="1">
-        <v>0.077586206896551699</v>
+        <v>0.067693059628543398</v>
       </c>
       <c r="I36" s="1">
-        <v>0.17839943572998729</v>
+        <v>0.19989848015592829</v>
       </c>
       <c r="J36" s="1">
-        <v>0.077586206896551699</v>
+        <v>0.067693059628543398</v>
       </c>
     </row>
     <row r="37">
@@ -2503,31 +2530,31 @@
         <v>27</v>
       </c>
       <c r="B37" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C37" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D37" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E37" s="1">
-        <v>0.58791208791208793</v>
+        <v>0.7553763440860215</v>
       </c>
       <c r="F37" s="1">
         <v>22</v>
       </c>
       <c r="G37" s="1">
-        <v>0.65909090909090906</v>
+        <v>0.81818181818181823</v>
       </c>
       <c r="H37" s="1">
-        <v>0.0711788211788211</v>
+        <v>0.062805474095796704</v>
       </c>
       <c r="I37" s="1">
-        <v>0.18066817888897849</v>
+        <v>0.1006874707948905</v>
       </c>
       <c r="J37" s="1">
-        <v>0.0711788211788211</v>
+        <v>0.062805474095796704</v>
       </c>
     </row>
     <row r="38">
@@ -2535,31 +2562,31 @@
         <v>27</v>
       </c>
       <c r="B38" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C38" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D38" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E38" s="1">
-        <v>0.75549450549450547</v>
+        <v>0.45161290322580638</v>
       </c>
       <c r="F38" s="1">
         <v>22</v>
       </c>
       <c r="G38" s="1">
-        <v>0.81818181818181823</v>
+        <v>0.5</v>
       </c>
       <c r="H38" s="1">
-        <v>0.062687312687312799</v>
+        <v>0.048387096774193603</v>
       </c>
       <c r="I38" s="1">
-        <v>0.097676700796505006</v>
+        <v>0.68538806215625137</v>
       </c>
       <c r="J38" s="1">
-        <v>0.062687312687312799</v>
+        <v>0.048387096774193603</v>
       </c>
     </row>
     <row r="39">
@@ -2567,31 +2594,31 @@
         <v>27</v>
       </c>
       <c r="B39" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C39" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D39" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E39" s="1">
-        <v>0.45054945054945062</v>
+        <v>0.043010752688171998</v>
       </c>
       <c r="F39" s="1">
         <v>22</v>
       </c>
       <c r="G39" s="1">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H39" s="1">
-        <v>0.0494505494505494</v>
+        <v>-0.043010752688171998</v>
       </c>
       <c r="I39" s="1">
-        <v>0.67951067214355387</v>
+        <v>0.32639522542870719</v>
       </c>
       <c r="J39" s="1">
-        <v>0.0494505494505494</v>
+        <v>0.043010752688171998</v>
       </c>
     </row>
     <row r="40">
@@ -2599,31 +2626,31 @@
         <v>27</v>
       </c>
       <c r="B40" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C40" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D40" s="1">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E40" s="1">
-        <v>0.043956043956044001</v>
+        <v>0.6713483146067416</v>
       </c>
       <c r="F40" s="1">
         <v>22</v>
       </c>
       <c r="G40" s="1">
-        <v>0</v>
+        <v>0.70454545454545459</v>
       </c>
       <c r="H40" s="1">
-        <v>-0.043956043956044001</v>
+        <v>0.033197139938712997</v>
       </c>
       <c r="I40" s="1">
-        <v>0.32103413173416762</v>
+        <v>0.5585600308312344</v>
       </c>
       <c r="J40" s="1">
-        <v>0.043956043956044001</v>
+        <v>0.033197139938712997</v>
       </c>
     </row>
     <row r="41">
@@ -2631,31 +2658,31 @@
         <v>27</v>
       </c>
       <c r="B41" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C41" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D41" s="1">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E41" s="1">
-        <v>0.66954022988505746</v>
+        <v>0.61955237837247956</v>
       </c>
       <c r="F41" s="1">
         <v>22</v>
       </c>
       <c r="G41" s="1">
-        <v>0.70454545454545459</v>
+        <v>0.65224689380689105</v>
       </c>
       <c r="H41" s="1">
-        <v>0.0350052246603971</v>
+        <v>0.0326945154344115</v>
       </c>
       <c r="I41" s="1">
-        <v>0.53748817890029621</v>
+        <v>0.2240407417593582</v>
       </c>
       <c r="J41" s="1">
-        <v>0.0350052246603971</v>
+        <v>0.0326945154344115</v>
       </c>
     </row>
     <row r="42">
@@ -2663,31 +2690,31 @@
         <v>27</v>
       </c>
       <c r="B42" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C42" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D42" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E42" s="1">
-        <v>0.6187458378928048</v>
+        <v>0.1075268817204301</v>
       </c>
       <c r="F42" s="1">
         <v>22</v>
       </c>
       <c r="G42" s="1">
-        <v>0.65224689380689105</v>
+        <v>0.090909090909090898</v>
       </c>
       <c r="H42" s="1">
-        <v>0.033501055914086302</v>
+        <v>-0.016617790811339201</v>
       </c>
       <c r="I42" s="1">
-        <v>0.21233908220317699</v>
+        <v>0.82057849198008404</v>
       </c>
       <c r="J42" s="1">
-        <v>0.033501055914086302</v>
+        <v>0.016617790811339201</v>
       </c>
     </row>
     <row r="43">
@@ -2695,31 +2722,31 @@
         <v>27</v>
       </c>
       <c r="B43" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C43" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D43" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E43" s="1">
-        <v>0.6187458378928048</v>
+        <v>0.60394265286384086</v>
       </c>
       <c r="F43" s="1">
         <v>22</v>
       </c>
       <c r="G43" s="1">
-        <v>0.65224689380689105</v>
+        <v>0.61742424016649078</v>
       </c>
       <c r="H43" s="1">
-        <v>0.033501055914086302</v>
+        <v>0.0134815873026499</v>
       </c>
       <c r="I43" s="1">
-        <v>0.21233908220317699</v>
+        <v>0.69693320030264905</v>
       </c>
       <c r="J43" s="1">
-        <v>0.033501055914086302</v>
+        <v>0.0134815873026499</v>
       </c>
     </row>
     <row r="44">
@@ -2727,127 +2754,127 @@
         <v>27</v>
       </c>
       <c r="B44" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C44" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D44" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E44" s="1">
-        <v>0.12087912087912089</v>
+        <v>0.40860215053763438</v>
       </c>
       <c r="F44" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G44" s="1">
-        <v>0.090909090909090898</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="H44" s="1">
-        <v>-0.029970029970029999</v>
+        <v>0.0080645161290322995</v>
       </c>
       <c r="I44" s="1">
-        <v>0.69572766973562561</v>
+        <v>0.8901728565194712</v>
       </c>
       <c r="J44" s="1">
-        <v>0.029970029970029999</v>
+        <v>0.0080645161290322995</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B45" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C45" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D45" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E45" s="1">
-        <v>0.60293040301773571</v>
+        <v>0.29032258064516131</v>
       </c>
       <c r="F45" s="1">
         <v>22</v>
       </c>
       <c r="G45" s="1">
-        <v>0.61742424016649078</v>
+        <v>0.77272727272727271</v>
       </c>
       <c r="H45" s="1">
-        <v>0.014493837148755099</v>
+        <v>0.4824046920821114</v>
       </c>
       <c r="I45" s="1">
-        <v>0.67300812961515244</v>
+        <v>1.6085554625300001e-05</v>
       </c>
       <c r="J45" s="1">
-        <v>0.014493837148755099</v>
+        <v>0.4824046920821114</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B46" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C46" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D46" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E46" s="1">
-        <v>0.60293040301773571</v>
+        <v>0.25806451612903231</v>
       </c>
       <c r="F46" s="1">
         <v>22</v>
       </c>
       <c r="G46" s="1">
-        <v>0.61742424016649078</v>
+        <v>0.59090909090909094</v>
       </c>
       <c r="H46" s="1">
-        <v>0.014493837148755099</v>
+        <v>0.33284457478005858</v>
       </c>
       <c r="I46" s="1">
-        <v>0.67300812961515244</v>
+        <v>0.0024169278216036</v>
       </c>
       <c r="J46" s="1">
-        <v>0.014493837148755099</v>
+        <v>0.33284457478005858</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B47" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C47" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D47" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E47" s="1">
-        <v>0.40659340659340659</v>
+        <v>0.096774193548387094</v>
       </c>
       <c r="F47" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G47" s="1">
-        <v>0.41666666666666669</v>
+        <v>0.36363636363636359</v>
       </c>
       <c r="H47" s="1">
-        <v>0.0100732600732601</v>
+        <v>0.26686217008797652</v>
       </c>
       <c r="I47" s="1">
-        <v>0.86306942797487096</v>
+        <v>0.0013326767126349999</v>
       </c>
       <c r="J47" s="1">
-        <v>0.0100732600732601</v>
+        <v>0.26686217008797652</v>
       </c>
     </row>
     <row r="48">
@@ -2855,127 +2882,127 @@
         <v>28</v>
       </c>
       <c r="B48" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C48" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D48" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E48" s="1">
-        <v>0.2967032967032967</v>
+        <v>0.086021505376344107</v>
       </c>
       <c r="F48" s="1">
         <v>22</v>
       </c>
       <c r="G48" s="1">
-        <v>0.77272727272727271</v>
+        <v>0.090909090909090898</v>
       </c>
       <c r="H48" s="1">
-        <v>0.476023976023976</v>
+        <v>0.0048875855327467996</v>
       </c>
       <c r="I48" s="1">
-        <v>2.3469505292300001e-05</v>
+        <v>0.94231045207869979</v>
       </c>
       <c r="J48" s="1">
-        <v>0.476023976023976</v>
+        <v>0.0048875855327467996</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B49" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C49" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D49" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E49" s="1">
-        <v>0.25274725274725268</v>
+        <v>4</v>
       </c>
       <c r="F49" s="1">
         <v>22</v>
       </c>
       <c r="G49" s="1">
-        <v>0.59090909090909094</v>
+        <v>8.2727272727272734</v>
       </c>
       <c r="H49" s="1">
-        <v>0.33816183816183831</v>
+        <v>4.2727272727272734</v>
       </c>
       <c r="I49" s="1">
-        <v>0.0020264466138074999</v>
+        <v>0.0090474062123942992</v>
       </c>
       <c r="J49" s="1">
-        <v>0.33816183816183831</v>
+        <v>4.2727272727272734</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B50" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C50" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D50" s="1">
         <v>91</v>
       </c>
       <c r="E50" s="1">
-        <v>0.087912087912087905</v>
+        <v>2.0109890109890109</v>
       </c>
       <c r="F50" s="1">
         <v>22</v>
       </c>
       <c r="G50" s="1">
-        <v>0.36363636363636359</v>
+        <v>2.7272727272727271</v>
       </c>
       <c r="H50" s="1">
-        <v>0.27572427572427571</v>
+        <v>0.71628371628371612</v>
       </c>
       <c r="I50" s="1">
-        <v>0.00073214846816179997</v>
+        <v>0.25150845040241671</v>
       </c>
       <c r="J50" s="1">
-        <v>0.27572427572427571</v>
+        <v>0.71628371628371612</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B51" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C51" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D51" s="1">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E51" s="1">
-        <v>0.0769230769230769</v>
+        <v>0.1797752808988764</v>
       </c>
       <c r="F51" s="1">
         <v>22</v>
       </c>
       <c r="G51" s="1">
-        <v>0.090909090909090898</v>
+        <v>0.72727272727272729</v>
       </c>
       <c r="H51" s="1">
-        <v>0.013986013986014</v>
+        <v>0.54749744637385089</v>
       </c>
       <c r="I51" s="1">
-        <v>0.82973704019732786</v>
+        <v>8.5955347447900004e-08</v>
       </c>
       <c r="J51" s="1">
-        <v>0.013986013986014</v>
+        <v>0.54749744637385089</v>
       </c>
     </row>
     <row r="52">
@@ -2983,31 +3010,31 @@
         <v>29</v>
       </c>
       <c r="B52" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C52" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D52" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E52" s="1">
-        <v>3.9890109890109891</v>
+        <v>16.473118279569889</v>
       </c>
       <c r="F52" s="1">
         <v>22</v>
       </c>
       <c r="G52" s="1">
-        <v>8.2727272727272734</v>
+        <v>16.77272727272727</v>
       </c>
       <c r="H52" s="1">
-        <v>4.2837162837162843</v>
+        <v>0.29960899315738132</v>
       </c>
       <c r="I52" s="1">
-        <v>0.0096158830162452001</v>
+        <v>0.91612233912068242</v>
       </c>
       <c r="J52" s="1">
-        <v>4.2837162837162843</v>
+        <v>0.29960899315738132</v>
       </c>
     </row>
     <row r="53">
@@ -3015,31 +3042,31 @@
         <v>29</v>
       </c>
       <c r="B53" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C53" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D53" s="1">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E53" s="1">
-        <v>1.966292134831461</v>
+        <v>0.68817204301075274</v>
       </c>
       <c r="F53" s="1">
         <v>22</v>
       </c>
       <c r="G53" s="1">
-        <v>2.7272727272727271</v>
+        <v>0.95454545454545459</v>
       </c>
       <c r="H53" s="1">
-        <v>0.76098059244126604</v>
+        <v>0.26637341153470179</v>
       </c>
       <c r="I53" s="1">
-        <v>0.22299404482387469</v>
+        <v>0.0102296368574016</v>
       </c>
       <c r="J53" s="1">
-        <v>0.76098059244126604</v>
+        <v>0.26637341153470179</v>
       </c>
     </row>
     <row r="54">
@@ -3047,31 +3074,31 @@
         <v>29</v>
       </c>
       <c r="B54" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C54" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D54" s="1">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E54" s="1">
-        <v>0.17241379310344829</v>
+        <v>0.23655913978494619</v>
       </c>
       <c r="F54" s="1">
         <v>22</v>
       </c>
       <c r="G54" s="1">
-        <v>0.72727272727272729</v>
+        <v>0.45454545454545447</v>
       </c>
       <c r="H54" s="1">
-        <v>0.55485893416927901</v>
+        <v>0.21798631476050831</v>
       </c>
       <c r="I54" s="1">
-        <v>4.9138475410000001e-08</v>
+        <v>0.13545150145885931</v>
       </c>
       <c r="J54" s="1">
-        <v>0.55485893416927901</v>
+        <v>0.21798631476050831</v>
       </c>
     </row>
     <row r="55">
@@ -3079,31 +3106,31 @@
         <v>29</v>
       </c>
       <c r="B55" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C55" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D55" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E55" s="1">
-        <v>16.428571428571431</v>
+        <v>0.4946236559139785</v>
       </c>
       <c r="F55" s="1">
         <v>22</v>
       </c>
       <c r="G55" s="1">
-        <v>16.77272727272727</v>
+        <v>0.68181818181818177</v>
       </c>
       <c r="H55" s="1">
-        <v>0.34415584415583922</v>
+        <v>0.1871945259042033</v>
       </c>
       <c r="I55" s="1">
-        <v>0.90494741084516028</v>
+        <v>0.11561778958311481</v>
       </c>
       <c r="J55" s="1">
-        <v>0.34415584415583922</v>
+        <v>0.1871945259042033</v>
       </c>
     </row>
     <row r="56">
@@ -3111,31 +3138,31 @@
         <v>29</v>
       </c>
       <c r="B56" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C56" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D56" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E56" s="1">
-        <v>0.68131868131868134</v>
+        <v>0.15053763440860221</v>
       </c>
       <c r="F56" s="1">
         <v>22</v>
       </c>
       <c r="G56" s="1">
-        <v>0.95454545454545459</v>
+        <v>0.31818181818181818</v>
       </c>
       <c r="H56" s="1">
-        <v>0.27322677322677319</v>
+        <v>0.16764418377321599</v>
       </c>
       <c r="I56" s="1">
-        <v>0.0089135821853709007</v>
+        <v>0.068199407286870906</v>
       </c>
       <c r="J56" s="1">
-        <v>0.27322677322677319</v>
+        <v>0.16764418377321599</v>
       </c>
     </row>
     <row r="57">
@@ -3143,31 +3170,31 @@
         <v>29</v>
       </c>
       <c r="B57" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C57" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D57" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E57" s="1">
-        <v>0.24175824175824179</v>
+        <v>0.27956989247311831</v>
       </c>
       <c r="F57" s="1">
         <v>22</v>
       </c>
       <c r="G57" s="1">
-        <v>0.45454545454545447</v>
+        <v>0.13636363636363641</v>
       </c>
       <c r="H57" s="1">
-        <v>0.21278721278721269</v>
+        <v>-0.1432062561094819</v>
       </c>
       <c r="I57" s="1">
-        <v>0.14885190668082149</v>
+        <v>0.16709101446404301</v>
       </c>
       <c r="J57" s="1">
-        <v>0.21278721278721269</v>
+        <v>0.1432062561094819</v>
       </c>
     </row>
     <row r="58">
@@ -3175,31 +3202,31 @@
         <v>29</v>
       </c>
       <c r="B58" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C58" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D58" s="1">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E58" s="1">
-        <v>0.49450549450549453</v>
+        <v>0.36467861848296629</v>
       </c>
       <c r="F58" s="1">
         <v>22</v>
       </c>
       <c r="G58" s="1">
-        <v>0.68181818181818177</v>
+        <v>0.43251508592417681</v>
       </c>
       <c r="H58" s="1">
-        <v>0.18731268731268719</v>
+        <v>0.067836467441210496</v>
       </c>
       <c r="I58" s="1">
-        <v>0.11616979064872091</v>
+        <v>0.025255136421771698</v>
       </c>
       <c r="J58" s="1">
-        <v>0.18731268731268719</v>
+        <v>0.067836467441210496</v>
       </c>
     </row>
     <row r="59">
@@ -3207,31 +3234,31 @@
         <v>29</v>
       </c>
       <c r="B59" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C59" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D59" s="1">
         <v>91</v>
       </c>
       <c r="E59" s="1">
-        <v>0.14285714285714279</v>
+        <v>0.043956043956044001</v>
       </c>
       <c r="F59" s="1">
         <v>22</v>
       </c>
       <c r="G59" s="1">
-        <v>0.31818181818181818</v>
+        <v>0.090909090909090898</v>
       </c>
       <c r="H59" s="1">
-        <v>0.17532467532467541</v>
+        <v>0.046953046953046897</v>
       </c>
       <c r="I59" s="1">
-        <v>0.053832803855205003</v>
+        <v>0.38261207526358898</v>
       </c>
       <c r="J59" s="1">
-        <v>0.17532467532467541</v>
+        <v>0.046953046953046897</v>
       </c>
     </row>
     <row r="60">
@@ -3239,31 +3266,31 @@
         <v>29</v>
       </c>
       <c r="B60" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C60" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D60" s="1">
         <v>91</v>
       </c>
       <c r="E60" s="1">
-        <v>0.26373626373626369</v>
+        <v>0.043956043956044001</v>
       </c>
       <c r="F60" s="1">
         <v>22</v>
       </c>
       <c r="G60" s="1">
-        <v>0.13636363636363641</v>
+        <v>0.090909090909090898</v>
       </c>
       <c r="H60" s="1">
-        <v>-0.12737262737262731</v>
+        <v>0.046953046953046897</v>
       </c>
       <c r="I60" s="1">
-        <v>0.21216301738709181</v>
+        <v>0.38261207526358898</v>
       </c>
       <c r="J60" s="1">
-        <v>0.12737262737262731</v>
+        <v>0.046953046953046897</v>
       </c>
     </row>
     <row r="61">
@@ -3271,80 +3298,80 @@
         <v>29</v>
       </c>
       <c r="B61" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C61" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D61" s="1">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E61" s="1">
-        <v>0.36216209716209708</v>
+        <v>0.978494623655914</v>
       </c>
       <c r="F61" s="1">
         <v>22</v>
       </c>
       <c r="G61" s="1">
-        <v>0.43251508592417681</v>
+        <v>1</v>
       </c>
       <c r="H61" s="1">
-        <v>0.070352988762079696</v>
+        <v>0.021505376344085999</v>
       </c>
       <c r="I61" s="1">
-        <v>0.0220712700010481</v>
+        <v>0.49205977192767397</v>
       </c>
       <c r="J61" s="1">
-        <v>0.070352988762079696</v>
+        <v>0.021505376344085999</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B62" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C62" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D62" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E62" s="1">
-        <v>0.043956043956044001</v>
+        <v>2.301075268817204</v>
       </c>
       <c r="F62" s="1">
         <v>22</v>
       </c>
       <c r="G62" s="1">
-        <v>0.090909090909090898</v>
+        <v>1.5909090909090911</v>
       </c>
       <c r="H62" s="1">
-        <v>0.046953046953046897</v>
+        <v>-0.71016617790811298</v>
       </c>
       <c r="I62" s="1">
-        <v>0.38261207526358898</v>
+        <v>0.0019609477212618001</v>
       </c>
       <c r="J62" s="1">
-        <v>0.046953046953046897</v>
+        <v>0.71016617790811298</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B63" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C63" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D63" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E63" s="1">
-        <v>0.043956043956044001</v>
+        <v>0.55913978494623651</v>
       </c>
       <c r="F63" s="1">
         <v>22</v>
@@ -3353,45 +3380,45 @@
         <v>0.090909090909090898</v>
       </c>
       <c r="H63" s="1">
-        <v>0.046953046953046897</v>
+        <v>-0.46823069403714562</v>
       </c>
       <c r="I63" s="1">
-        <v>0.38261207526358898</v>
+        <v>4.94375614732e-05</v>
       </c>
       <c r="J63" s="1">
-        <v>0.046953046953046897</v>
+        <v>0.46823069403714562</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B64" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C64" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D64" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E64" s="1">
-        <v>0.97802197802197799</v>
+        <v>0.76344086021505375</v>
       </c>
       <c r="F64" s="1">
         <v>22</v>
       </c>
       <c r="G64" s="1">
-        <v>1</v>
+        <v>0.45454545454545447</v>
       </c>
       <c r="H64" s="1">
-        <v>0.021978021978022001</v>
+        <v>-0.30889540566959928</v>
       </c>
       <c r="I64" s="1">
-        <v>0.48733919649206342</v>
+        <v>0.0040265127730818003</v>
       </c>
       <c r="J64" s="1">
-        <v>0.021978021978022001</v>
+        <v>0.30889540566959928</v>
       </c>
     </row>
     <row r="65">
@@ -3399,31 +3426,31 @@
         <v>30</v>
       </c>
       <c r="B65" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C65" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D65" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E65" s="1">
-        <v>2.285714285714286</v>
+        <v>0.68817204301075274</v>
       </c>
       <c r="F65" s="1">
         <v>22</v>
       </c>
       <c r="G65" s="1">
-        <v>1.5909090909090911</v>
+        <v>0.93181818181818177</v>
       </c>
       <c r="H65" s="1">
-        <v>-0.69480519480519498</v>
+        <v>0.243646138807429</v>
       </c>
       <c r="I65" s="1">
-        <v>0.0025864446227961998</v>
+        <v>0.0037286887679765998</v>
       </c>
       <c r="J65" s="1">
-        <v>0.69480519480519498</v>
+        <v>0.243646138807429</v>
       </c>
     </row>
     <row r="66">
@@ -3431,31 +3458,31 @@
         <v>30</v>
       </c>
       <c r="B66" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C66" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D66" s="1">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="E66" s="1">
-        <v>0.53846153846153844</v>
+        <v>0.55434782608695654</v>
       </c>
       <c r="F66" s="1">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G66" s="1">
-        <v>0.090909090909090898</v>
+        <v>0.77631578947368418</v>
       </c>
       <c r="H66" s="1">
-        <v>-0.44755244755244761</v>
+        <v>0.22196796338672761</v>
       </c>
       <c r="I66" s="1">
-        <v>0.00010829431630969999</v>
+        <v>0.0013141839603253999</v>
       </c>
       <c r="J66" s="1">
-        <v>0.44755244755244761</v>
+        <v>0.22196796338672761</v>
       </c>
     </row>
     <row r="67">
@@ -3463,31 +3490,31 @@
         <v>30</v>
       </c>
       <c r="B67" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C67" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D67" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E67" s="1">
-        <v>0.75824175824175821</v>
+        <v>0.5161290322580645</v>
       </c>
       <c r="F67" s="1">
         <v>22</v>
       </c>
       <c r="G67" s="1">
-        <v>0.45454545454545447</v>
+        <v>0.72727272727272729</v>
       </c>
       <c r="H67" s="1">
-        <v>-0.30369630369630368</v>
+        <v>0.21114369501466279</v>
       </c>
       <c r="I67" s="1">
-        <v>0.0050254356935673997</v>
+        <v>0.074149097587517005</v>
       </c>
       <c r="J67" s="1">
-        <v>0.30369630369630368</v>
+        <v>0.21114369501466279</v>
       </c>
     </row>
     <row r="68">
@@ -3495,31 +3522,31 @@
         <v>30</v>
       </c>
       <c r="B68" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C68" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D68" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E68" s="1">
-        <v>0.68681318681318682</v>
+        <v>0.52456441365422746</v>
       </c>
       <c r="F68" s="1">
         <v>22</v>
       </c>
       <c r="G68" s="1">
-        <v>0.93181818181818177</v>
+        <v>0.71448863636363635</v>
       </c>
       <c r="H68" s="1">
-        <v>0.24500499500499501</v>
+        <v>0.1899242227094089</v>
       </c>
       <c r="I68" s="1">
-        <v>0.0037600823987185999</v>
+        <v>0.00070536868281790004</v>
       </c>
       <c r="J68" s="1">
-        <v>0.24500499500499501</v>
+        <v>0.1899242227094089</v>
       </c>
     </row>
     <row r="69">
@@ -3527,31 +3554,31 @@
         <v>30</v>
       </c>
       <c r="B69" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C69" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D69" s="1">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="E69" s="1">
-        <v>0.55223880597014929</v>
+        <v>0.53763440860215051</v>
       </c>
       <c r="F69" s="1">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G69" s="1">
-        <v>0.77631578947368418</v>
+        <v>0.72727272727272729</v>
       </c>
       <c r="H69" s="1">
-        <v>0.22407698350353489</v>
+        <v>0.18963831867057679</v>
       </c>
       <c r="I69" s="1">
-        <v>0.0013517296258888001</v>
+        <v>0.1075943763256744</v>
       </c>
       <c r="J69" s="1">
-        <v>0.22407698350353489</v>
+        <v>0.18963831867057679</v>
       </c>
     </row>
     <row r="70">
@@ -3559,31 +3586,31 @@
         <v>30</v>
       </c>
       <c r="B70" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C70" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D70" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E70" s="1">
-        <v>0.51648351648351654</v>
+        <v>0.5053763440860215</v>
       </c>
       <c r="F70" s="1">
         <v>22</v>
       </c>
       <c r="G70" s="1">
-        <v>0.72727272727272729</v>
+        <v>0.63636363636363635</v>
       </c>
       <c r="H70" s="1">
-        <v>0.21078921078921081</v>
+        <v>0.13098729227761491</v>
       </c>
       <c r="I70" s="1">
-        <v>0.075214504306689606</v>
+        <v>0.27224935160037622</v>
       </c>
       <c r="J70" s="1">
-        <v>0.21078921078921081</v>
+        <v>0.13098729227761491</v>
       </c>
     </row>
     <row r="71">
@@ -3591,31 +3618,31 @@
         <v>30</v>
       </c>
       <c r="B71" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C71" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D71" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E71" s="1">
-        <v>0.52304385131695763</v>
+        <v>0.5268817204301075</v>
       </c>
       <c r="F71" s="1">
         <v>22</v>
       </c>
       <c r="G71" s="1">
-        <v>0.71448863636363635</v>
+        <v>0.63636363636363635</v>
       </c>
       <c r="H71" s="1">
-        <v>0.19144478504667869</v>
+        <v>0.10948191593352891</v>
       </c>
       <c r="I71" s="1">
-        <v>0.00071198271501949999</v>
+        <v>0.35787189970000383</v>
       </c>
       <c r="J71" s="1">
-        <v>0.19144478504667869</v>
+        <v>0.10948191593352891</v>
       </c>
     </row>
     <row r="72">
@@ -3623,31 +3650,31 @@
         <v>30</v>
       </c>
       <c r="B72" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C72" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D72" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E72" s="1">
-        <v>0.52304385131695763</v>
+        <v>0.54973118808320776</v>
       </c>
       <c r="F72" s="1">
         <v>22</v>
       </c>
       <c r="G72" s="1">
-        <v>0.71448863636363635</v>
+        <v>0.6549873846498403</v>
       </c>
       <c r="H72" s="1">
-        <v>0.19144478504667869</v>
+        <v>0.1052561965666325</v>
       </c>
       <c r="I72" s="1">
-        <v>0.00071198271501949999</v>
+        <v>0.21503700877172391</v>
       </c>
       <c r="J72" s="1">
-        <v>0.19144478504667869</v>
+        <v>0.1052561965666325</v>
       </c>
     </row>
     <row r="73">
@@ -3655,31 +3682,31 @@
         <v>30</v>
       </c>
       <c r="B73" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C73" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D73" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E73" s="1">
-        <v>0.53846153846153844</v>
+        <v>0.53763440860215051</v>
       </c>
       <c r="F73" s="1">
         <v>22</v>
       </c>
       <c r="G73" s="1">
-        <v>0.72727272727272729</v>
+        <v>0.63636363636363635</v>
       </c>
       <c r="H73" s="1">
-        <v>0.18881118881118891</v>
+        <v>0.098729227761485794</v>
       </c>
       <c r="I73" s="1">
-        <v>0.1097985927780615</v>
+        <v>0.40633414267841389</v>
       </c>
       <c r="J73" s="1">
-        <v>0.18881118881118891</v>
+        <v>0.098729227761485794</v>
       </c>
     </row>
     <row r="74">
@@ -3687,31 +3714,31 @@
         <v>30</v>
       </c>
       <c r="B74" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C74" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D74" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E74" s="1">
-        <v>0.50549450549450547</v>
+        <v>0.69959678268560799</v>
       </c>
       <c r="F74" s="1">
         <v>22</v>
       </c>
       <c r="G74" s="1">
-        <v>0.63636363636363635</v>
+        <v>0.75931188193234533</v>
       </c>
       <c r="H74" s="1">
-        <v>0.13086913086913091</v>
+        <v>0.059715099246737298</v>
       </c>
       <c r="I74" s="1">
-        <v>0.27373558683540788</v>
+        <v>0.25757373456635108</v>
       </c>
       <c r="J74" s="1">
-        <v>0.13086913086913091</v>
+        <v>0.059715099246737298</v>
       </c>
     </row>
     <row r="75">
@@ -3719,31 +3746,31 @@
         <v>30</v>
       </c>
       <c r="B75" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C75" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D75" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E75" s="1">
-        <v>0.52747252747252749</v>
+        <v>0.31989247311827962</v>
       </c>
       <c r="F75" s="1">
         <v>22</v>
       </c>
       <c r="G75" s="1">
-        <v>0.63636363636363635</v>
+        <v>0.35606060606060602</v>
       </c>
       <c r="H75" s="1">
-        <v>0.1088911088911089</v>
+        <v>0.036168132942326403</v>
       </c>
       <c r="I75" s="1">
-        <v>0.36149197990439819</v>
+        <v>0.50804299508562245</v>
       </c>
       <c r="J75" s="1">
-        <v>0.1088911088911089</v>
+        <v>0.036168132942326403</v>
       </c>
     </row>
     <row r="76">
@@ -3751,31 +3778,31 @@
         <v>30</v>
       </c>
       <c r="B76" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C76" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D76" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E76" s="1">
-        <v>0.54990843003922763</v>
+        <v>0.84946236559139787</v>
       </c>
       <c r="F76" s="1">
         <v>22</v>
       </c>
       <c r="G76" s="1">
-        <v>0.6549873846498403</v>
+        <v>0.86363636363636365</v>
       </c>
       <c r="H76" s="1">
-        <v>0.1050789546106127</v>
+        <v>0.0141739980449658</v>
       </c>
       <c r="I76" s="1">
-        <v>0.21430643662257179</v>
+        <v>0.86767335157620629</v>
       </c>
       <c r="J76" s="1">
-        <v>0.1050789546106127</v>
+        <v>0.0141739980449658</v>
       </c>
     </row>
     <row r="77">
@@ -3783,31 +3810,31 @@
         <v>30</v>
       </c>
       <c r="B77" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C77" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="D77" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E77" s="1">
-        <v>0.53846153846153844</v>
+        <v>0.31182795698924731</v>
       </c>
       <c r="F77" s="1">
         <v>22</v>
       </c>
       <c r="G77" s="1">
-        <v>0.63636363636363635</v>
+        <v>0.31818181818181818</v>
       </c>
       <c r="H77" s="1">
-        <v>0.097902097902097904</v>
+        <v>0.0063538611925708999</v>
       </c>
       <c r="I77" s="1">
-        <v>0.41124505860639249</v>
+        <v>0.95441616004135088</v>
       </c>
       <c r="J77" s="1">
-        <v>0.097902097902097904</v>
+        <v>0.0063538611925708999</v>
       </c>
     </row>
     <row r="78">
@@ -3815,191 +3842,31 @@
         <v>30</v>
       </c>
       <c r="B78" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C78" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D78" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E78" s="1">
-        <v>0.69803114464649785</v>
+        <v>0.77419354838709675</v>
       </c>
       <c r="F78" s="1">
         <v>22</v>
       </c>
       <c r="G78" s="1">
-        <v>0.75931188193234533</v>
+        <v>0.77272727272727271</v>
       </c>
       <c r="H78" s="1">
-        <v>0.0612807372858475</v>
+        <v>-0.0014662756598240001</v>
       </c>
       <c r="I78" s="1">
-        <v>0.24579374673905729</v>
+        <v>0.9883321736490267</v>
       </c>
       <c r="J78" s="1">
-        <v>0.0612807372858475</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s">
-        <v>30</v>
-      </c>
-      <c r="B79" t="s">
-        <v>104</v>
-      </c>
-      <c r="C79" t="s">
-        <v>181</v>
-      </c>
-      <c r="D79" s="1">
-        <v>91</v>
-      </c>
-      <c r="E79" s="1">
-        <v>0.69803114464649785</v>
-      </c>
-      <c r="F79" s="1">
-        <v>22</v>
-      </c>
-      <c r="G79" s="1">
-        <v>0.75931188193234533</v>
-      </c>
-      <c r="H79" s="1">
-        <v>0.0612807372858475</v>
-      </c>
-      <c r="I79" s="1">
-        <v>0.24579374673905729</v>
-      </c>
-      <c r="J79" s="1">
-        <v>0.0612807372858475</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s">
-        <v>30</v>
-      </c>
-      <c r="B80" t="s">
-        <v>105</v>
-      </c>
-      <c r="C80" t="s">
-        <v>182</v>
-      </c>
-      <c r="D80" s="1">
-        <v>91</v>
-      </c>
-      <c r="E80" s="1">
-        <v>0.3177655677655678</v>
-      </c>
-      <c r="F80" s="1">
-        <v>22</v>
-      </c>
-      <c r="G80" s="1">
-        <v>0.35606060606060602</v>
-      </c>
-      <c r="H80" s="1">
-        <v>0.038295038295038199</v>
-      </c>
-      <c r="I80" s="1">
-        <v>0.47928736223762791</v>
-      </c>
-      <c r="J80" s="1">
-        <v>0.038295038295038199</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s">
-        <v>30</v>
-      </c>
-      <c r="B81" t="s">
-        <v>106</v>
-      </c>
-      <c r="C81" t="s">
-        <v>183</v>
-      </c>
-      <c r="D81" s="1">
-        <v>91</v>
-      </c>
-      <c r="E81" s="1">
-        <v>0.84615384615384615</v>
-      </c>
-      <c r="F81" s="1">
-        <v>22</v>
-      </c>
-      <c r="G81" s="1">
-        <v>0.86363636363636365</v>
-      </c>
-      <c r="H81" s="1">
-        <v>0.017482517482517501</v>
-      </c>
-      <c r="I81" s="1">
-        <v>0.83869457181096274</v>
-      </c>
-      <c r="J81" s="1">
-        <v>0.017482517482517501</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s">
-        <v>30</v>
-      </c>
-      <c r="B82" t="s">
-        <v>107</v>
-      </c>
-      <c r="C82" t="s">
-        <v>184</v>
-      </c>
-      <c r="D82" s="1">
-        <v>91</v>
-      </c>
-      <c r="E82" s="1">
-        <v>0.30769230769230771</v>
-      </c>
-      <c r="F82" s="1">
-        <v>22</v>
-      </c>
-      <c r="G82" s="1">
-        <v>0.31818181818181818</v>
-      </c>
-      <c r="H82" s="1">
-        <v>0.0104895104895105</v>
-      </c>
-      <c r="I82" s="1">
-        <v>0.9247696454183334</v>
-      </c>
-      <c r="J82" s="1">
-        <v>0.0104895104895105</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s">
-        <v>30</v>
-      </c>
-      <c r="B83" t="s">
-        <v>108</v>
-      </c>
-      <c r="C83" t="s">
-        <v>185</v>
-      </c>
-      <c r="D83" s="1">
-        <v>91</v>
-      </c>
-      <c r="E83" s="1">
-        <v>0.78021978021978022</v>
-      </c>
-      <c r="F83" s="1">
-        <v>22</v>
-      </c>
-      <c r="G83" s="1">
-        <v>0.77272727272727271</v>
-      </c>
-      <c r="H83" s="1">
-        <v>-0.0074925074925074999</v>
-      </c>
-      <c r="I83" s="1">
-        <v>0.94010805705080525</v>
-      </c>
-      <c r="J83" s="1">
-        <v>0.0074925074925074999</v>
+        <v>0.0014662756598240001</v>
       </c>
     </row>
   </sheetData>
@@ -4008,7 +3875,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J83"/>
+  <dimension ref="A1:J78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4054,10 +3921,10 @@
         <v>156</v>
       </c>
       <c r="D2" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E2" s="1">
-        <v>3.9890109890109891</v>
+        <v>4</v>
       </c>
       <c r="F2" s="1">
         <v>22</v>
@@ -4066,13 +3933,13 @@
         <v>8.2727272727272734</v>
       </c>
       <c r="H2" s="1">
-        <v>4.2837162837162843</v>
+        <v>4.2727272727272734</v>
       </c>
       <c r="I2" s="1">
-        <v>0.0096158830162452001</v>
+        <v>0.0090474062123942992</v>
       </c>
       <c r="J2" s="1">
-        <v>4.2837162837162843</v>
+        <v>4.2727272727272734</v>
       </c>
     </row>
     <row r="3">
@@ -4086,10 +3953,10 @@
         <v>157</v>
       </c>
       <c r="D3" s="1">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E3" s="1">
-        <v>1.966292134831461</v>
+        <v>2.0109890109890109</v>
       </c>
       <c r="F3" s="1">
         <v>22</v>
@@ -4098,13 +3965,13 @@
         <v>2.7272727272727271</v>
       </c>
       <c r="H3" s="1">
-        <v>0.76098059244126604</v>
+        <v>0.71628371628371612</v>
       </c>
       <c r="I3" s="1">
-        <v>0.22299404482387469</v>
+        <v>0.25150845040241671</v>
       </c>
       <c r="J3" s="1">
-        <v>0.76098059244126604</v>
+        <v>0.71628371628371612</v>
       </c>
     </row>
     <row r="4">
@@ -4118,10 +3985,10 @@
         <v>169</v>
       </c>
       <c r="D4" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E4" s="1">
-        <v>2.285714285714286</v>
+        <v>2.301075268817204</v>
       </c>
       <c r="F4" s="1">
         <v>22</v>
@@ -4130,13 +3997,13 @@
         <v>1.5909090909090911</v>
       </c>
       <c r="H4" s="1">
-        <v>-0.69480519480519498</v>
+        <v>-0.71016617790811298</v>
       </c>
       <c r="I4" s="1">
-        <v>0.0025864446227961998</v>
+        <v>0.0019609477212618001</v>
       </c>
       <c r="J4" s="1">
-        <v>0.69480519480519498</v>
+        <v>0.71016617790811298</v>
       </c>
     </row>
     <row r="5">
@@ -4150,10 +4017,10 @@
         <v>158</v>
       </c>
       <c r="D5" s="1">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E5" s="1">
-        <v>0.17241379310344829</v>
+        <v>0.1797752808988764</v>
       </c>
       <c r="F5" s="1">
         <v>22</v>
@@ -4162,13 +4029,13 @@
         <v>0.72727272727272729</v>
       </c>
       <c r="H5" s="1">
-        <v>0.55485893416927901</v>
+        <v>0.54749744637385089</v>
       </c>
       <c r="I5" s="1">
-        <v>4.9138475410000001e-08</v>
+        <v>8.5955347447900004e-08</v>
       </c>
       <c r="J5" s="1">
-        <v>0.55485893416927901</v>
+        <v>0.54749744637385089</v>
       </c>
     </row>
     <row r="6">
@@ -4182,10 +4049,10 @@
         <v>152</v>
       </c>
       <c r="D6" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E6" s="1">
-        <v>0.2967032967032967</v>
+        <v>0.29032258064516131</v>
       </c>
       <c r="F6" s="1">
         <v>22</v>
@@ -4194,13 +4061,13 @@
         <v>0.77272727272727271</v>
       </c>
       <c r="H6" s="1">
-        <v>0.476023976023976</v>
+        <v>0.4824046920821114</v>
       </c>
       <c r="I6" s="1">
-        <v>2.3469505292300001e-05</v>
+        <v>1.6085554625300001e-05</v>
       </c>
       <c r="J6" s="1">
-        <v>0.476023976023976</v>
+        <v>0.4824046920821114</v>
       </c>
     </row>
     <row r="7">
@@ -4214,10 +4081,10 @@
         <v>170</v>
       </c>
       <c r="D7" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E7" s="1">
-        <v>0.53846153846153844</v>
+        <v>0.55913978494623651</v>
       </c>
       <c r="F7" s="1">
         <v>22</v>
@@ -4226,109 +4093,109 @@
         <v>0.090909090909090898</v>
       </c>
       <c r="H7" s="1">
-        <v>-0.44755244755244761</v>
+        <v>-0.46823069403714562</v>
       </c>
       <c r="I7" s="1">
-        <v>0.00010829431630969999</v>
+        <v>4.94375614732e-05</v>
       </c>
       <c r="J7" s="1">
-        <v>0.44755244755244761</v>
+        <v>0.46823069403714562</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="D8" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E8" s="1">
-        <v>16.428571428571431</v>
+        <v>0.25806451612903231</v>
       </c>
       <c r="F8" s="1">
         <v>22</v>
       </c>
       <c r="G8" s="1">
-        <v>16.77272727272727</v>
+        <v>0.59090909090909094</v>
       </c>
       <c r="H8" s="1">
-        <v>0.34415584415583922</v>
+        <v>0.33284457478005858</v>
       </c>
       <c r="I8" s="1">
-        <v>0.90494741084516028</v>
+        <v>0.0024169278216036</v>
       </c>
       <c r="J8" s="1">
-        <v>0.34415584415583922</v>
+        <v>0.33284457478005858</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C9" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D9" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E9" s="1">
-        <v>0.25274725274725268</v>
+        <v>0.76344086021505375</v>
       </c>
       <c r="F9" s="1">
         <v>22</v>
       </c>
       <c r="G9" s="1">
-        <v>0.59090909090909094</v>
+        <v>0.45454545454545447</v>
       </c>
       <c r="H9" s="1">
-        <v>0.33816183816183831</v>
+        <v>-0.30889540566959928</v>
       </c>
       <c r="I9" s="1">
-        <v>0.0020264466138074999</v>
+        <v>0.0040265127730818003</v>
       </c>
       <c r="J9" s="1">
-        <v>0.33816183816183831</v>
+        <v>0.30889540566959928</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="D10" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E10" s="1">
-        <v>0.75824175824175821</v>
+        <v>16.473118279569889</v>
       </c>
       <c r="F10" s="1">
         <v>22</v>
       </c>
       <c r="G10" s="1">
-        <v>0.45454545454545447</v>
+        <v>16.77272727272727</v>
       </c>
       <c r="H10" s="1">
-        <v>-0.30369630369630368</v>
+        <v>0.29960899315738132</v>
       </c>
       <c r="I10" s="1">
-        <v>0.0050254356935673997</v>
+        <v>0.91612233912068242</v>
       </c>
       <c r="J10" s="1">
-        <v>0.30369630369630368</v>
+        <v>0.29960899315738132</v>
       </c>
     </row>
     <row r="11">
@@ -4342,10 +4209,10 @@
         <v>154</v>
       </c>
       <c r="D11" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E11" s="1">
-        <v>0.087912087912087905</v>
+        <v>0.096774193548387094</v>
       </c>
       <c r="F11" s="1">
         <v>22</v>
@@ -4354,13 +4221,13 @@
         <v>0.36363636363636359</v>
       </c>
       <c r="H11" s="1">
-        <v>0.27572427572427571</v>
+        <v>0.26686217008797652</v>
       </c>
       <c r="I11" s="1">
-        <v>0.00073214846816179997</v>
+        <v>0.0013326767126349999</v>
       </c>
       <c r="J11" s="1">
-        <v>0.27572427572427571</v>
+        <v>0.26686217008797652</v>
       </c>
     </row>
     <row r="12">
@@ -4374,10 +4241,10 @@
         <v>160</v>
       </c>
       <c r="D12" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E12" s="1">
-        <v>0.68131868131868134</v>
+        <v>0.68817204301075274</v>
       </c>
       <c r="F12" s="1">
         <v>22</v>
@@ -4386,13 +4253,13 @@
         <v>0.95454545454545459</v>
       </c>
       <c r="H12" s="1">
-        <v>0.27322677322677319</v>
+        <v>0.26637341153470179</v>
       </c>
       <c r="I12" s="1">
-        <v>0.0089135821853709007</v>
+        <v>0.0102296368574016</v>
       </c>
       <c r="J12" s="1">
-        <v>0.27322677322677319</v>
+        <v>0.26637341153470179</v>
       </c>
     </row>
     <row r="13">
@@ -4406,10 +4273,10 @@
         <v>172</v>
       </c>
       <c r="D13" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E13" s="1">
-        <v>0.68681318681318682</v>
+        <v>0.68817204301075274</v>
       </c>
       <c r="F13" s="1">
         <v>22</v>
@@ -4418,13 +4285,13 @@
         <v>0.93181818181818177</v>
       </c>
       <c r="H13" s="1">
-        <v>0.24500499500499501</v>
+        <v>0.243646138807429</v>
       </c>
       <c r="I13" s="1">
-        <v>0.0037600823987185999</v>
+        <v>0.0037286887679765998</v>
       </c>
       <c r="J13" s="1">
-        <v>0.24500499500499501</v>
+        <v>0.243646138807429</v>
       </c>
     </row>
     <row r="14">
@@ -4438,10 +4305,10 @@
         <v>173</v>
       </c>
       <c r="D14" s="1">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E14" s="1">
-        <v>0.55223880597014929</v>
+        <v>0.55434782608695654</v>
       </c>
       <c r="F14" s="1">
         <v>19</v>
@@ -4450,109 +4317,109 @@
         <v>0.77631578947368418</v>
       </c>
       <c r="H14" s="1">
-        <v>0.22407698350353489</v>
+        <v>0.22196796338672761</v>
       </c>
       <c r="I14" s="1">
-        <v>0.0013517296258888001</v>
+        <v>0.0013141839603253999</v>
       </c>
       <c r="J14" s="1">
-        <v>0.22407698350353489</v>
+        <v>0.22196796338672761</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>84</v>
       </c>
       <c r="C15" t="s">
-        <v>118</v>
+        <v>161</v>
       </c>
       <c r="D15" s="1">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E15" s="1">
-        <v>0.45170454545454553</v>
+        <v>0.23655913978494619</v>
       </c>
       <c r="F15" s="1">
         <v>22</v>
       </c>
       <c r="G15" s="1">
-        <v>0.67045454545454541</v>
+        <v>0.45454545454545447</v>
       </c>
       <c r="H15" s="1">
-        <v>0.21874999999999989</v>
+        <v>0.21798631476050831</v>
       </c>
       <c r="I15" s="1">
-        <v>0.0011524680243634</v>
+        <v>0.13545150145885931</v>
       </c>
       <c r="J15" s="1">
-        <v>0.21874999999999989</v>
+        <v>0.21798631476050831</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="C16" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="D16" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E16" s="1">
-        <v>0.24175824175824179</v>
+        <v>0.5161290322580645</v>
       </c>
       <c r="F16" s="1">
         <v>22</v>
       </c>
       <c r="G16" s="1">
-        <v>0.45454545454545447</v>
+        <v>0.72727272727272729</v>
       </c>
       <c r="H16" s="1">
-        <v>0.21278721278721269</v>
+        <v>0.21114369501466279</v>
       </c>
       <c r="I16" s="1">
-        <v>0.14885190668082149</v>
+        <v>0.074149097587517005</v>
       </c>
       <c r="J16" s="1">
-        <v>0.21278721278721269</v>
+        <v>0.21114369501466279</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B17" t="s">
-        <v>97</v>
+        <v>41</v>
       </c>
       <c r="C17" t="s">
-        <v>174</v>
+        <v>118</v>
       </c>
       <c r="D17" s="1">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E17" s="1">
-        <v>0.51648351648351654</v>
+        <v>0.46111111111111108</v>
       </c>
       <c r="F17" s="1">
         <v>22</v>
       </c>
       <c r="G17" s="1">
-        <v>0.72727272727272729</v>
+        <v>0.67045454545454541</v>
       </c>
       <c r="H17" s="1">
-        <v>0.21078921078921081</v>
+        <v>0.2093434343434343</v>
       </c>
       <c r="I17" s="1">
-        <v>0.075214504306689606</v>
+        <v>0.0018960041074505001</v>
       </c>
       <c r="J17" s="1">
-        <v>0.21078921078921081</v>
+        <v>0.2093434343434343</v>
       </c>
     </row>
     <row r="18">
@@ -4566,10 +4433,10 @@
         <v>175</v>
       </c>
       <c r="D18" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E18" s="1">
-        <v>0.52304385131695763</v>
+        <v>0.52456441365422746</v>
       </c>
       <c r="F18" s="1">
         <v>22</v>
@@ -4578,13 +4445,13 @@
         <v>0.71448863636363635</v>
       </c>
       <c r="H18" s="1">
-        <v>0.19144478504667869</v>
+        <v>0.1899242227094089</v>
       </c>
       <c r="I18" s="1">
-        <v>0.00071198271501949999</v>
+        <v>0.00070536868281790004</v>
       </c>
       <c r="J18" s="1">
-        <v>0.19144478504667869</v>
+        <v>0.1899242227094089</v>
       </c>
     </row>
     <row r="19">
@@ -4592,159 +4459,159 @@
         <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C19" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D19" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E19" s="1">
-        <v>0.52304385131695763</v>
+        <v>0.53763440860215051</v>
       </c>
       <c r="F19" s="1">
         <v>22</v>
       </c>
       <c r="G19" s="1">
-        <v>0.71448863636363635</v>
+        <v>0.72727272727272729</v>
       </c>
       <c r="H19" s="1">
-        <v>0.19144478504667869</v>
+        <v>0.18963831867057679</v>
       </c>
       <c r="I19" s="1">
-        <v>0.00071198271501949999</v>
+        <v>0.1075943763256744</v>
       </c>
       <c r="J19" s="1">
-        <v>0.19144478504667869</v>
+        <v>0.18963831867057679</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="C20" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="D20" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E20" s="1">
-        <v>0.53846153846153844</v>
+        <v>0.4946236559139785</v>
       </c>
       <c r="F20" s="1">
         <v>22</v>
       </c>
       <c r="G20" s="1">
-        <v>0.72727272727272729</v>
+        <v>0.68181818181818177</v>
       </c>
       <c r="H20" s="1">
-        <v>0.18881118881118891</v>
+        <v>0.1871945259042033</v>
       </c>
       <c r="I20" s="1">
-        <v>0.1097985927780615</v>
+        <v>0.11561778958311481</v>
       </c>
       <c r="J20" s="1">
-        <v>0.18881118881118891</v>
+        <v>0.1871945259042033</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="C21" t="s">
-        <v>162</v>
+        <v>119</v>
       </c>
       <c r="D21" s="1">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E21" s="1">
-        <v>0.49450549450549453</v>
+        <v>0.42222222222222222</v>
       </c>
       <c r="F21" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G21" s="1">
-        <v>0.68181818181818177</v>
+        <v>0.6071428571428571</v>
       </c>
       <c r="H21" s="1">
-        <v>0.18731268731268719</v>
+        <v>0.1849206349206349</v>
       </c>
       <c r="I21" s="1">
-        <v>0.11616979064872091</v>
+        <v>0.0082921406870097008</v>
       </c>
       <c r="J21" s="1">
-        <v>0.18731268731268719</v>
+        <v>0.1849206349206349</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="C22" t="s">
-        <v>119</v>
+        <v>163</v>
       </c>
       <c r="D22" s="1">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E22" s="1">
-        <v>0.42897727272727271</v>
+        <v>0.15053763440860221</v>
       </c>
       <c r="F22" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G22" s="1">
-        <v>0.6071428571428571</v>
+        <v>0.31818181818181818</v>
       </c>
       <c r="H22" s="1">
-        <v>0.17816558441558439</v>
+        <v>0.16764418377321599</v>
       </c>
       <c r="I22" s="1">
-        <v>0.011995828540544</v>
+        <v>0.068199407286870906</v>
       </c>
       <c r="J22" s="1">
-        <v>0.17816558441558439</v>
+        <v>0.16764418377321599</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B23" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="C23" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="D23" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E23" s="1">
-        <v>0.14285714285714279</v>
+        <v>0.30107526881720431</v>
       </c>
       <c r="F23" s="1">
         <v>22</v>
       </c>
       <c r="G23" s="1">
-        <v>0.31818181818181818</v>
+        <v>0.13636363636363641</v>
       </c>
       <c r="H23" s="1">
-        <v>0.17532467532467541</v>
+        <v>-0.1647116324535679</v>
       </c>
       <c r="I23" s="1">
-        <v>0.053832803855205003</v>
+        <v>0.11948466631400551</v>
       </c>
       <c r="J23" s="1">
-        <v>0.17532467532467541</v>
+        <v>0.1647116324535679</v>
       </c>
     </row>
     <row r="24">
@@ -4752,95 +4619,95 @@
         <v>27</v>
       </c>
       <c r="B24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C24" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D24" s="1">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E24" s="1">
-        <v>0.2967032967032967</v>
+        <v>0.5252808988764045</v>
       </c>
       <c r="F24" s="1">
         <v>22</v>
       </c>
       <c r="G24" s="1">
-        <v>0.13636363636363641</v>
+        <v>0.375</v>
       </c>
       <c r="H24" s="1">
-        <v>-0.16033966033966029</v>
+        <v>-0.1502808988764045</v>
       </c>
       <c r="I24" s="1">
-        <v>0.1287057679630938</v>
+        <v>0.038062927313723197</v>
       </c>
       <c r="J24" s="1">
-        <v>0.16033966033966029</v>
+        <v>0.1502808988764045</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B25" t="s">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="D25" s="1">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E25" s="1">
-        <v>0.52011494252873558</v>
+        <v>0.27956989247311831</v>
       </c>
       <c r="F25" s="1">
         <v>22</v>
       </c>
       <c r="G25" s="1">
-        <v>0.375</v>
+        <v>0.13636363636363641</v>
       </c>
       <c r="H25" s="1">
-        <v>-0.14511494252873561</v>
+        <v>-0.1432062561094819</v>
       </c>
       <c r="I25" s="1">
-        <v>0.043689650194955701</v>
+        <v>0.16709101446404301</v>
       </c>
       <c r="J25" s="1">
-        <v>0.14511494252873561</v>
+        <v>0.1432062561094819</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B26" t="s">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="C26" t="s">
-        <v>110</v>
+        <v>177</v>
       </c>
       <c r="D26" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E26" s="1">
-        <v>0.67648417707327957</v>
+        <v>0.5053763440860215</v>
       </c>
       <c r="F26" s="1">
         <v>22</v>
       </c>
       <c r="G26" s="1">
-        <v>0.80842424793676892</v>
+        <v>0.63636363636363635</v>
       </c>
       <c r="H26" s="1">
-        <v>0.13194007086348941</v>
+        <v>0.13098729227761491</v>
       </c>
       <c r="I26" s="1">
-        <v>1.51330004656e-05</v>
+        <v>0.27224935160037622</v>
       </c>
       <c r="J26" s="1">
-        <v>0.13194007086348941</v>
+        <v>0.13098729227761491</v>
       </c>
     </row>
     <row r="27">
@@ -4854,10 +4721,10 @@
         <v>137</v>
       </c>
       <c r="D27" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E27" s="1">
-        <v>0.59615384615384615</v>
+        <v>0.59677419354838712</v>
       </c>
       <c r="F27" s="1">
         <v>22</v>
@@ -4866,45 +4733,45 @@
         <v>0.72727272727272729</v>
       </c>
       <c r="H27" s="1">
-        <v>0.13111888111888109</v>
+        <v>0.1304985337243402</v>
       </c>
       <c r="I27" s="1">
-        <v>0.0112288864446566</v>
+        <v>0.010965617038097701</v>
       </c>
       <c r="J27" s="1">
-        <v>0.13111888111888109</v>
+        <v>0.1304985337243402</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>177</v>
+        <v>110</v>
       </c>
       <c r="D28" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E28" s="1">
-        <v>0.50549450549450547</v>
+        <v>0.67828619063541451</v>
       </c>
       <c r="F28" s="1">
         <v>22</v>
       </c>
       <c r="G28" s="1">
-        <v>0.63636363636363635</v>
+        <v>0.80842424793676892</v>
       </c>
       <c r="H28" s="1">
-        <v>0.13086913086913091</v>
+        <v>0.13013805730135439</v>
       </c>
       <c r="I28" s="1">
-        <v>0.27373558683540788</v>
+        <v>1.9104368201999999e-05</v>
       </c>
       <c r="J28" s="1">
-        <v>0.13086913086913091</v>
+        <v>0.13013805730135439</v>
       </c>
     </row>
     <row r="29">
@@ -4918,10 +4785,10 @@
         <v>113</v>
       </c>
       <c r="D29" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E29" s="1">
-        <v>0.76128336263226937</v>
+        <v>0.76238479569394102</v>
       </c>
       <c r="F29" s="1">
         <v>22</v>
@@ -4930,45 +4797,45 @@
         <v>0.89157197421247314</v>
       </c>
       <c r="H29" s="1">
-        <v>0.1302886115802038</v>
+        <v>0.12918717851853209</v>
       </c>
       <c r="I29" s="1">
-        <v>0.00020955452112240001</v>
+        <v>0.00024086750106500001</v>
       </c>
       <c r="J29" s="1">
-        <v>0.1302886115802038</v>
+        <v>0.12918717851853209</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B30" t="s">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="C30" t="s">
-        <v>164</v>
+        <v>120</v>
       </c>
       <c r="D30" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E30" s="1">
-        <v>0.26373626373626369</v>
+        <v>0.83870967741935487</v>
       </c>
       <c r="F30" s="1">
         <v>22</v>
       </c>
       <c r="G30" s="1">
-        <v>0.13636363636363641</v>
+        <v>0.95454545454545459</v>
       </c>
       <c r="H30" s="1">
-        <v>-0.12737262737262731</v>
+        <v>0.1158357771260997</v>
       </c>
       <c r="I30" s="1">
-        <v>0.21216301738709181</v>
+        <v>0.1607752812799218</v>
       </c>
       <c r="J30" s="1">
-        <v>0.12737262737262731</v>
+        <v>0.1158357771260997</v>
       </c>
     </row>
     <row r="31">
@@ -4976,31 +4843,31 @@
         <v>26</v>
       </c>
       <c r="B31" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C31" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D31" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E31" s="1">
-        <v>0.8351648351648352</v>
+        <v>0.43010752688172038</v>
       </c>
       <c r="F31" s="1">
         <v>22</v>
       </c>
       <c r="G31" s="1">
-        <v>0.95454545454545459</v>
+        <v>0.54545454545454541</v>
       </c>
       <c r="H31" s="1">
-        <v>0.1193806193806194</v>
+        <v>0.11534701857282501</v>
       </c>
       <c r="I31" s="1">
-        <v>0.15216897342503741</v>
+        <v>0.3326032191300492</v>
       </c>
       <c r="J31" s="1">
-        <v>0.1193806193806194</v>
+        <v>0.11534701857282501</v>
       </c>
     </row>
     <row r="32">
@@ -5014,10 +4881,10 @@
         <v>178</v>
       </c>
       <c r="D32" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E32" s="1">
-        <v>0.52747252747252749</v>
+        <v>0.5268817204301075</v>
       </c>
       <c r="F32" s="1">
         <v>22</v>
@@ -5026,13 +4893,13 @@
         <v>0.63636363636363635</v>
       </c>
       <c r="H32" s="1">
-        <v>0.1088911088911089</v>
+        <v>0.10948191593352891</v>
       </c>
       <c r="I32" s="1">
-        <v>0.36149197990439819</v>
+        <v>0.35787189970000383</v>
       </c>
       <c r="J32" s="1">
-        <v>0.1088911088911089</v>
+        <v>0.10948191593352891</v>
       </c>
     </row>
     <row r="33">
@@ -5046,10 +4913,10 @@
         <v>179</v>
       </c>
       <c r="D33" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E33" s="1">
-        <v>0.54990843003922763</v>
+        <v>0.54973118808320776</v>
       </c>
       <c r="F33" s="1">
         <v>22</v>
@@ -5058,13 +4925,13 @@
         <v>0.6549873846498403</v>
       </c>
       <c r="H33" s="1">
-        <v>0.1050789546106127</v>
+        <v>0.1052561965666325</v>
       </c>
       <c r="I33" s="1">
-        <v>0.21430643662257179</v>
+        <v>0.21503700877172391</v>
       </c>
       <c r="J33" s="1">
-        <v>0.1050789546106127</v>
+        <v>0.1052561965666325</v>
       </c>
     </row>
     <row r="34">
@@ -5078,10 +4945,10 @@
         <v>114</v>
       </c>
       <c r="D34" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E34" s="1">
-        <v>0.65477272647095253</v>
+        <v>0.65486559055505256</v>
       </c>
       <c r="F34" s="1">
         <v>22</v>
@@ -5090,141 +4957,141 @@
         <v>0.75867769257588824</v>
       </c>
       <c r="H34" s="1">
-        <v>0.1039049661049357</v>
+        <v>0.1038121020208357</v>
       </c>
       <c r="I34" s="1">
-        <v>0.023254832145028301</v>
+        <v>0.022014726228919299</v>
       </c>
       <c r="J34" s="1">
-        <v>0.1039049661049357</v>
+        <v>0.1038121020208357</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B35" t="s">
-        <v>61</v>
+        <v>103</v>
       </c>
       <c r="C35" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="D35" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E35" s="1">
-        <v>0.59340659340659341</v>
+        <v>0.53763440860215051</v>
       </c>
       <c r="F35" s="1">
         <v>22</v>
       </c>
       <c r="G35" s="1">
-        <v>0.69318181818181823</v>
+        <v>0.63636363636363635</v>
       </c>
       <c r="H35" s="1">
-        <v>0.099775224775224797</v>
+        <v>0.098729227761485794</v>
       </c>
       <c r="I35" s="1">
-        <v>0.057697490578584601</v>
+        <v>0.40633414267841389</v>
       </c>
       <c r="J35" s="1">
-        <v>0.099775224775224797</v>
+        <v>0.098729227761485794</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>103</v>
+        <v>61</v>
       </c>
       <c r="C36" t="s">
-        <v>180</v>
+        <v>138</v>
       </c>
       <c r="D36" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E36" s="1">
-        <v>0.53846153846153844</v>
+        <v>0.59677419354838712</v>
       </c>
       <c r="F36" s="1">
         <v>22</v>
       </c>
       <c r="G36" s="1">
-        <v>0.63636363636363635</v>
+        <v>0.69318181818181823</v>
       </c>
       <c r="H36" s="1">
-        <v>0.097902097902097904</v>
+        <v>0.096407624633431097</v>
       </c>
       <c r="I36" s="1">
-        <v>0.41124505860639249</v>
+        <v>0.064734462072081403</v>
       </c>
       <c r="J36" s="1">
-        <v>0.097902097902097904</v>
+        <v>0.096407624633431097</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B37" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="C37" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="D37" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E37" s="1">
-        <v>0.45054945054945062</v>
+        <v>0.086021505376344107</v>
       </c>
       <c r="F37" s="1">
         <v>22</v>
       </c>
       <c r="G37" s="1">
-        <v>0.54545454545454541</v>
+        <v>0</v>
       </c>
       <c r="H37" s="1">
-        <v>0.0949050949050948</v>
+        <v>-0.086021505376344107</v>
       </c>
       <c r="I37" s="1">
-        <v>0.4279525320297285</v>
+        <v>0.15651386444400159</v>
       </c>
       <c r="J37" s="1">
-        <v>0.0949050949050948</v>
+        <v>0.086021505376344107</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B38" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="C38" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="D38" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E38" s="1">
-        <v>0.087912087912087905</v>
+        <v>0.68817204301075274</v>
       </c>
       <c r="F38" s="1">
         <v>22</v>
       </c>
       <c r="G38" s="1">
-        <v>0</v>
+        <v>0.77272727272727271</v>
       </c>
       <c r="H38" s="1">
-        <v>-0.087912087912087905</v>
+        <v>0.084555229716520006</v>
       </c>
       <c r="I38" s="1">
-        <v>0.1517681784726721</v>
+        <v>0.43890215547745593</v>
       </c>
       <c r="J38" s="1">
-        <v>0.087912087912087905</v>
+        <v>0.084555229716520006</v>
       </c>
     </row>
     <row r="39">
@@ -5232,16 +5099,16 @@
         <v>26</v>
       </c>
       <c r="B39" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C39" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D39" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E39" s="1">
-        <v>0.61510880062213313</v>
+        <v>0.615209507205153</v>
       </c>
       <c r="F39" s="1">
         <v>22</v>
@@ -5250,45 +5117,45 @@
         <v>0.69829996065659961</v>
       </c>
       <c r="H39" s="1">
-        <v>0.083191160034466499</v>
+        <v>0.083090453451446597</v>
       </c>
       <c r="I39" s="1">
-        <v>0.025535190366513801</v>
+        <v>0.023705043506038501</v>
       </c>
       <c r="J39" s="1">
-        <v>0.083191160034466499</v>
+        <v>0.083090453451446597</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B40" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="C40" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="D40" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E40" s="1">
-        <v>0.61510880062213313</v>
+        <v>0.61021505376344087</v>
       </c>
       <c r="F40" s="1">
         <v>22</v>
       </c>
       <c r="G40" s="1">
-        <v>0.69829996065659961</v>
+        <v>0.69318181818181823</v>
       </c>
       <c r="H40" s="1">
-        <v>0.083191160034466499</v>
+        <v>0.082966764418377401</v>
       </c>
       <c r="I40" s="1">
-        <v>0.025535190366513801</v>
+        <v>0.11299979230854509</v>
       </c>
       <c r="J40" s="1">
-        <v>0.083191160034466499</v>
+        <v>0.082966764418377401</v>
       </c>
     </row>
     <row r="41">
@@ -5296,223 +5163,223 @@
         <v>27</v>
       </c>
       <c r="B41" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C41" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D41" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E41" s="1">
-        <v>0.61263736263736268</v>
+        <v>0.59946236559139787</v>
       </c>
       <c r="F41" s="1">
         <v>22</v>
       </c>
       <c r="G41" s="1">
-        <v>0.69318181818181823</v>
+        <v>0.68181818181818177</v>
       </c>
       <c r="H41" s="1">
-        <v>0.080544455544455607</v>
+        <v>0.082355816226783896</v>
       </c>
       <c r="I41" s="1">
-        <v>0.12273202904129769</v>
+        <v>0.081563711558646695</v>
       </c>
       <c r="J41" s="1">
-        <v>0.080544455544455607</v>
+        <v>0.082355816226783896</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="C42" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="D42" s="1">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E42" s="1">
-        <v>0.69230769230769229</v>
+        <v>0.6713483146067416</v>
       </c>
       <c r="F42" s="1">
         <v>22</v>
       </c>
       <c r="G42" s="1">
-        <v>0.77272727272727271</v>
+        <v>0.75</v>
       </c>
       <c r="H42" s="1">
-        <v>0.080419580419580403</v>
+        <v>0.078651685393258397</v>
       </c>
       <c r="I42" s="1">
-        <v>0.46107928367593493</v>
+        <v>0.17307573740344351</v>
       </c>
       <c r="J42" s="1">
-        <v>0.080419580419580403</v>
+        <v>0.078651685393258397</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B43" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="C43" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="D43" s="1">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="E43" s="1">
-        <v>0.60164835164835162</v>
+        <v>0.6875</v>
       </c>
       <c r="F43" s="1">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G43" s="1">
-        <v>0.68181818181818177</v>
+        <v>0.76470588235294113</v>
       </c>
       <c r="H43" s="1">
-        <v>0.080169830169830106</v>
+        <v>0.077205882352941096</v>
       </c>
       <c r="I43" s="1">
-        <v>0.088129803214070601</v>
+        <v>0.49698882369010422</v>
       </c>
       <c r="J43" s="1">
-        <v>0.080169830169830106</v>
+        <v>0.077205882352941096</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B44" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C44" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D44" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E44" s="1">
-        <v>0.60798011621931092</v>
+        <v>0.64271773253717734</v>
       </c>
       <c r="F44" s="1">
         <v>22</v>
       </c>
       <c r="G44" s="1">
-        <v>0.68582250719720672</v>
+        <v>0.71757883917201648</v>
       </c>
       <c r="H44" s="1">
-        <v>0.077842390977895804</v>
+        <v>0.074861106634839095</v>
       </c>
       <c r="I44" s="1">
-        <v>0.022874150237429801</v>
+        <v>0.00054342656699579999</v>
       </c>
       <c r="J44" s="1">
-        <v>0.077842390977895804</v>
+        <v>0.074861106634839095</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B45" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="C45" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="D45" s="1">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E45" s="1">
-        <v>0.67241379310344829</v>
+        <v>0.4838709677419355</v>
       </c>
       <c r="F45" s="1">
         <v>22</v>
       </c>
       <c r="G45" s="1">
-        <v>0.75</v>
+        <v>0.40909090909090912</v>
       </c>
       <c r="H45" s="1">
-        <v>0.077586206896551699</v>
+        <v>-0.074780058651026396</v>
       </c>
       <c r="I45" s="1">
-        <v>0.17839943572998729</v>
+        <v>0.53154290901188228</v>
       </c>
       <c r="J45" s="1">
-        <v>0.077586206896551699</v>
+        <v>0.074780058651026396</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B46" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="C46" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="D46" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E46" s="1">
-        <v>0.58241758241758246</v>
+        <v>0.61169994950935402</v>
       </c>
       <c r="F46" s="1">
         <v>22</v>
       </c>
       <c r="G46" s="1">
-        <v>0.65909090909090906</v>
+        <v>0.68582250719720672</v>
       </c>
       <c r="H46" s="1">
-        <v>0.076673326673326603</v>
+        <v>0.074122557687852697</v>
       </c>
       <c r="I46" s="1">
-        <v>0.14808856021965239</v>
+        <v>0.029959187331934801</v>
       </c>
       <c r="J46" s="1">
-        <v>0.076673326673326603</v>
+        <v>0.074122557687852697</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B47" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="C47" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="D47" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E47" s="1">
-        <v>0.6410022639966273</v>
+        <v>0.58602150537634412</v>
       </c>
       <c r="F47" s="1">
         <v>22</v>
       </c>
       <c r="G47" s="1">
-        <v>0.71757883917201648</v>
+        <v>0.65909090909090906</v>
       </c>
       <c r="H47" s="1">
-        <v>0.076576575175389197</v>
+        <v>0.073069403714564898</v>
       </c>
       <c r="I47" s="1">
-        <v>0.00037670378643190001</v>
+        <v>0.16534088350526069</v>
       </c>
       <c r="J47" s="1">
-        <v>0.076576575175389197</v>
+        <v>0.073069403714564898</v>
       </c>
     </row>
     <row r="48">
@@ -5520,16 +5387,16 @@
         <v>26</v>
       </c>
       <c r="B48" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C48" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D48" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E48" s="1">
-        <v>0.87912087912087911</v>
+        <v>0.88172043010752688</v>
       </c>
       <c r="F48" s="1">
         <v>22</v>
@@ -5538,45 +5405,45 @@
         <v>0.95454545454545459</v>
       </c>
       <c r="H48" s="1">
-        <v>0.075424575424575493</v>
+        <v>0.072825024437927696</v>
       </c>
       <c r="I48" s="1">
-        <v>0.30705810298076669</v>
+        <v>0.31924939276812558</v>
       </c>
       <c r="J48" s="1">
-        <v>0.075424575424575493</v>
+        <v>0.072825024437927696</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="C49" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="D49" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E49" s="1">
-        <v>0.48351648351648352</v>
+        <v>0.66913728143579221</v>
       </c>
       <c r="F49" s="1">
         <v>22</v>
       </c>
       <c r="G49" s="1">
-        <v>0.40909090909090912</v>
+        <v>0.74123304946856061</v>
       </c>
       <c r="H49" s="1">
-        <v>-0.074425574425574403</v>
+        <v>0.072095768032768404</v>
       </c>
       <c r="I49" s="1">
-        <v>0.53440024041636403</v>
+        <v>0.015769077113338699</v>
       </c>
       <c r="J49" s="1">
-        <v>0.074425574425574403</v>
+        <v>0.072095768032768404</v>
       </c>
     </row>
     <row r="50">
@@ -5590,10 +5457,10 @@
         <v>116</v>
       </c>
       <c r="D50" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E50" s="1">
-        <v>0.74512531829404305</v>
+        <v>0.7479093616367668</v>
       </c>
       <c r="F50" s="1">
         <v>22</v>
@@ -5602,77 +5469,77 @@
         <v>0.81921211697838525</v>
       </c>
       <c r="H50" s="1">
-        <v>0.074086798684342203</v>
+        <v>0.071302755341618507</v>
       </c>
       <c r="I50" s="1">
-        <v>0.0142565558822026</v>
+        <v>0.019539672517746899</v>
       </c>
       <c r="J50" s="1">
-        <v>0.074086798684342203</v>
+        <v>0.071302755341618507</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B51" t="s">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="C51" t="s">
-        <v>127</v>
+        <v>165</v>
       </c>
       <c r="D51" s="1">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="E51" s="1">
-        <v>0.69090909090909092</v>
+        <v>0.36467861848296629</v>
       </c>
       <c r="F51" s="1">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G51" s="1">
-        <v>0.76470588235294113</v>
+        <v>0.43251508592417681</v>
       </c>
       <c r="H51" s="1">
-        <v>0.073796791443850193</v>
+        <v>0.067836467441210496</v>
       </c>
       <c r="I51" s="1">
-        <v>0.51936252607505184</v>
+        <v>0.025255136421771698</v>
       </c>
       <c r="J51" s="1">
-        <v>0.073796791443850193</v>
+        <v>0.067836467441210496</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B52" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="C52" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="D52" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E52" s="1">
-        <v>0.66870664927985646</v>
+        <v>0.59139784946236562</v>
       </c>
       <c r="F52" s="1">
         <v>22</v>
       </c>
       <c r="G52" s="1">
-        <v>0.74123304946856061</v>
+        <v>0.65909090909090906</v>
       </c>
       <c r="H52" s="1">
-        <v>0.072526400188704196</v>
+        <v>0.067693059628543398</v>
       </c>
       <c r="I52" s="1">
-        <v>0.015245241111370799</v>
+        <v>0.19989848015592829</v>
       </c>
       <c r="J52" s="1">
-        <v>0.072526400188704196</v>
+        <v>0.067693059628543398</v>
       </c>
     </row>
     <row r="53">
@@ -5680,191 +5547,191 @@
         <v>27</v>
       </c>
       <c r="B53" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C53" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D53" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E53" s="1">
-        <v>0.58791208791208793</v>
+        <v>0.7553763440860215</v>
       </c>
       <c r="F53" s="1">
         <v>22</v>
       </c>
       <c r="G53" s="1">
-        <v>0.65909090909090906</v>
+        <v>0.81818181818181823</v>
       </c>
       <c r="H53" s="1">
-        <v>0.0711788211788211</v>
+        <v>0.062805474095796704</v>
       </c>
       <c r="I53" s="1">
-        <v>0.18066817888897849</v>
+        <v>0.1006874707948905</v>
       </c>
       <c r="J53" s="1">
-        <v>0.0711788211788211</v>
+        <v>0.062805474095796704</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B54" t="s">
-        <v>88</v>
+        <v>51</v>
       </c>
       <c r="C54" t="s">
-        <v>165</v>
+        <v>128</v>
       </c>
       <c r="D54" s="1">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="E54" s="1">
-        <v>0.36216209716209708</v>
+        <v>0.71818181818181814</v>
       </c>
       <c r="F54" s="1">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G54" s="1">
-        <v>0.43251508592417681</v>
+        <v>0.65625</v>
       </c>
       <c r="H54" s="1">
-        <v>0.070352988762079696</v>
+        <v>-0.061931818181818102</v>
       </c>
       <c r="I54" s="1">
-        <v>0.0220712700010481</v>
+        <v>0.59880668484187516</v>
       </c>
       <c r="J54" s="1">
-        <v>0.070352988762079696</v>
+        <v>0.061931818181818102</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B55" t="s">
-        <v>51</v>
+        <v>104</v>
       </c>
       <c r="C55" t="s">
-        <v>128</v>
+        <v>181</v>
       </c>
       <c r="D55" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E55" s="1">
-        <v>0.2087912087912088</v>
+        <v>0.69959678268560799</v>
       </c>
       <c r="F55" s="1">
         <v>22</v>
       </c>
       <c r="G55" s="1">
-        <v>0.27272727272727271</v>
+        <v>0.75931188193234533</v>
       </c>
       <c r="H55" s="1">
-        <v>0.063936063936063894</v>
+        <v>0.059715099246737298</v>
       </c>
       <c r="I55" s="1">
-        <v>0.52104617563932409</v>
+        <v>0.25757373456635108</v>
       </c>
       <c r="J55" s="1">
-        <v>0.063936063936063894</v>
+        <v>0.059715099246737298</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B56" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="C56" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="D56" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E56" s="1">
-        <v>0.75549450549450547</v>
+        <v>0.21505376344086019</v>
       </c>
       <c r="F56" s="1">
         <v>22</v>
       </c>
       <c r="G56" s="1">
-        <v>0.81818181818181823</v>
+        <v>0.27272727272727271</v>
       </c>
       <c r="H56" s="1">
-        <v>0.062687312687312799</v>
+        <v>0.057673509286412503</v>
       </c>
       <c r="I56" s="1">
-        <v>0.097676700796505006</v>
+        <v>0.56486310795380701</v>
       </c>
       <c r="J56" s="1">
-        <v>0.062687312687312799</v>
+        <v>0.057673509286412503</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B57" t="s">
-        <v>104</v>
+        <v>53</v>
       </c>
       <c r="C57" t="s">
-        <v>181</v>
+        <v>130</v>
       </c>
       <c r="D57" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E57" s="1">
-        <v>0.69803114464649785</v>
+        <v>0.59408602150537637</v>
       </c>
       <c r="F57" s="1">
         <v>22</v>
       </c>
       <c r="G57" s="1">
-        <v>0.75931188193234533</v>
+        <v>0.64772727272727271</v>
       </c>
       <c r="H57" s="1">
-        <v>0.0612807372858475</v>
+        <v>0.053641251221896301</v>
       </c>
       <c r="I57" s="1">
-        <v>0.24579374673905729</v>
+        <v>0.28780031279951213</v>
       </c>
       <c r="J57" s="1">
-        <v>0.0612807372858475</v>
+        <v>0.053641251221896301</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B58" t="s">
-        <v>104</v>
+        <v>68</v>
       </c>
       <c r="C58" t="s">
-        <v>181</v>
+        <v>145</v>
       </c>
       <c r="D58" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E58" s="1">
-        <v>0.69803114464649785</v>
+        <v>0.45161290322580638</v>
       </c>
       <c r="F58" s="1">
         <v>22</v>
       </c>
       <c r="G58" s="1">
-        <v>0.75931188193234533</v>
+        <v>0.5</v>
       </c>
       <c r="H58" s="1">
-        <v>0.0612807372858475</v>
+        <v>0.048387096774193603</v>
       </c>
       <c r="I58" s="1">
-        <v>0.24579374673905729</v>
+        <v>0.68538806215625137</v>
       </c>
       <c r="J58" s="1">
-        <v>0.0612807372858475</v>
+        <v>0.048387096774193603</v>
       </c>
     </row>
     <row r="59">
@@ -5872,95 +5739,95 @@
         <v>26</v>
       </c>
       <c r="B59" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C59" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D59" s="1">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="E59" s="1">
-        <v>0.71698113207547165</v>
+        <v>0.702247191011236</v>
       </c>
       <c r="F59" s="1">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G59" s="1">
-        <v>0.65625</v>
+        <v>0.75</v>
       </c>
       <c r="H59" s="1">
-        <v>-0.060731132075471601</v>
+        <v>0.047752808988764002</v>
       </c>
       <c r="I59" s="1">
-        <v>0.61077787700083586</v>
+        <v>0.51920550288726419</v>
       </c>
       <c r="J59" s="1">
-        <v>0.060731132075471601</v>
+        <v>0.047752808988764002</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B60" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="C60" t="s">
-        <v>130</v>
+        <v>167</v>
       </c>
       <c r="D60" s="1">
         <v>91</v>
       </c>
       <c r="E60" s="1">
-        <v>0.59340659340659341</v>
+        <v>0.043956043956044001</v>
       </c>
       <c r="F60" s="1">
         <v>22</v>
       </c>
       <c r="G60" s="1">
-        <v>0.64772727272727271</v>
+        <v>0.090909090909090898</v>
       </c>
       <c r="H60" s="1">
-        <v>0.054320679320679299</v>
+        <v>0.046953046953046897</v>
       </c>
       <c r="I60" s="1">
-        <v>0.28551869536860558</v>
+        <v>0.38261207526358898</v>
       </c>
       <c r="J60" s="1">
-        <v>0.054320679320679299</v>
+        <v>0.046953046953046897</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B61" t="s">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="C61" t="s">
-        <v>131</v>
+        <v>166</v>
       </c>
       <c r="D61" s="1">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E61" s="1">
-        <v>0.69827586206896552</v>
+        <v>0.043956043956044001</v>
       </c>
       <c r="F61" s="1">
         <v>22</v>
       </c>
       <c r="G61" s="1">
-        <v>0.75</v>
+        <v>0.090909090909090898</v>
       </c>
       <c r="H61" s="1">
-        <v>0.051724137931034503</v>
+        <v>0.046953046953046897</v>
       </c>
       <c r="I61" s="1">
-        <v>0.48825865975192989</v>
+        <v>0.38261207526358898</v>
       </c>
       <c r="J61" s="1">
-        <v>0.051724137931034503</v>
+        <v>0.046953046953046897</v>
       </c>
     </row>
     <row r="62">
@@ -5968,319 +5835,319 @@
         <v>27</v>
       </c>
       <c r="B62" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C62" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D62" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E62" s="1">
-        <v>0.45054945054945062</v>
+        <v>0.043010752688171998</v>
       </c>
       <c r="F62" s="1">
         <v>22</v>
       </c>
       <c r="G62" s="1">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H62" s="1">
-        <v>0.0494505494505494</v>
+        <v>-0.043010752688171998</v>
       </c>
       <c r="I62" s="1">
-        <v>0.67951067214355387</v>
+        <v>0.32639522542870719</v>
       </c>
       <c r="J62" s="1">
-        <v>0.0494505494505494</v>
+        <v>0.043010752688171998</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B63" t="s">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="C63" t="s">
-        <v>167</v>
+        <v>117</v>
       </c>
       <c r="D63" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E63" s="1">
-        <v>0.043956043956044001</v>
+        <v>0.70687724249337314</v>
       </c>
       <c r="F63" s="1">
         <v>22</v>
       </c>
       <c r="G63" s="1">
-        <v>0.090909090909090898</v>
+        <v>0.7486426803198728</v>
       </c>
       <c r="H63" s="1">
-        <v>0.046953046953046897</v>
+        <v>0.041765437826499698</v>
       </c>
       <c r="I63" s="1">
-        <v>0.38261207526358898</v>
+        <v>0.19719782960896681</v>
       </c>
       <c r="J63" s="1">
-        <v>0.046953046953046897</v>
+        <v>0.041765437826499698</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B64" t="s">
-        <v>89</v>
+        <v>55</v>
       </c>
       <c r="C64" t="s">
-        <v>166</v>
+        <v>132</v>
       </c>
       <c r="D64" s="1">
         <v>91</v>
       </c>
       <c r="E64" s="1">
-        <v>0.043956043956044001</v>
+        <v>0.74725274725274726</v>
       </c>
       <c r="F64" s="1">
         <v>22</v>
       </c>
       <c r="G64" s="1">
-        <v>0.090909090909090898</v>
+        <v>0.78409090909090906</v>
       </c>
       <c r="H64" s="1">
-        <v>0.046953046953046897</v>
+        <v>0.036838161838161798</v>
       </c>
       <c r="I64" s="1">
-        <v>0.38261207526358898</v>
+        <v>0.59172546051504582</v>
       </c>
       <c r="J64" s="1">
-        <v>0.046953046953046897</v>
+        <v>0.036838161838161798</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B65" t="s">
-        <v>69</v>
+        <v>105</v>
       </c>
       <c r="C65" t="s">
-        <v>146</v>
+        <v>182</v>
       </c>
       <c r="D65" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E65" s="1">
-        <v>0.043956043956044001</v>
+        <v>0.31989247311827962</v>
       </c>
       <c r="F65" s="1">
         <v>22</v>
       </c>
       <c r="G65" s="1">
-        <v>0</v>
+        <v>0.35606060606060602</v>
       </c>
       <c r="H65" s="1">
-        <v>-0.043956043956044001</v>
+        <v>0.036168132942326403</v>
       </c>
       <c r="I65" s="1">
-        <v>0.32103413173416762</v>
+        <v>0.50804299508562245</v>
       </c>
       <c r="J65" s="1">
-        <v>0.043956043956044001</v>
+        <v>0.036168132942326403</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B66" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="C66" t="s">
-        <v>117</v>
+        <v>147</v>
       </c>
       <c r="D66" s="1">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E66" s="1">
-        <v>0.70691392185923818</v>
+        <v>0.6713483146067416</v>
       </c>
       <c r="F66" s="1">
         <v>22</v>
       </c>
       <c r="G66" s="1">
-        <v>0.7486426803198728</v>
+        <v>0.70454545454545459</v>
       </c>
       <c r="H66" s="1">
-        <v>0.041728758460634598</v>
+        <v>0.033197139938712997</v>
       </c>
       <c r="I66" s="1">
-        <v>0.19143151962259569</v>
+        <v>0.5585600308312344</v>
       </c>
       <c r="J66" s="1">
-        <v>0.041728758460634598</v>
+        <v>0.033197139938712997</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B67" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="C67" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="D67" s="1">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E67" s="1">
-        <v>0.7443820224719101</v>
+        <v>0.61955237837247956</v>
       </c>
       <c r="F67" s="1">
         <v>22</v>
       </c>
       <c r="G67" s="1">
-        <v>0.78409090909090906</v>
+        <v>0.65224689380689105</v>
       </c>
       <c r="H67" s="1">
-        <v>0.039708886618998997</v>
+        <v>0.0326945154344115</v>
       </c>
       <c r="I67" s="1">
-        <v>0.56625226823520469</v>
+        <v>0.2240407417593582</v>
       </c>
       <c r="J67" s="1">
-        <v>0.039708886618998997</v>
+        <v>0.0326945154344115</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B68" t="s">
-        <v>105</v>
+        <v>56</v>
       </c>
       <c r="C68" t="s">
-        <v>182</v>
+        <v>133</v>
       </c>
       <c r="D68" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E68" s="1">
-        <v>0.3177655677655678</v>
+        <v>0.5161290322580645</v>
       </c>
       <c r="F68" s="1">
         <v>22</v>
       </c>
       <c r="G68" s="1">
-        <v>0.35606060606060602</v>
+        <v>0.54545454545454541</v>
       </c>
       <c r="H68" s="1">
-        <v>0.038295038295038199</v>
+        <v>0.029325513196480898</v>
       </c>
       <c r="I68" s="1">
-        <v>0.47928736223762791</v>
+        <v>0.8064949829553979</v>
       </c>
       <c r="J68" s="1">
-        <v>0.038295038295038199</v>
+        <v>0.029325513196480898</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
+        <v>24</v>
+      </c>
+      <c r="B69" t="s">
+        <v>35</v>
+      </c>
+      <c r="C69" t="s">
         <v>27</v>
       </c>
-      <c r="B69" t="s">
-        <v>70</v>
-      </c>
-      <c r="C69" t="s">
-        <v>147</v>
-      </c>
       <c r="D69" s="1">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E69" s="1">
-        <v>0.66954022988505746</v>
+        <v>0.61174751417611239</v>
       </c>
       <c r="F69" s="1">
         <v>22</v>
       </c>
       <c r="G69" s="1">
-        <v>0.70454545454545459</v>
+        <v>0.6348355656320398</v>
       </c>
       <c r="H69" s="1">
-        <v>0.0350052246603971</v>
+        <v>0.023088051455927398</v>
       </c>
       <c r="I69" s="1">
-        <v>0.53748817890029621</v>
+        <v>0.39299283822349318</v>
       </c>
       <c r="J69" s="1">
-        <v>0.0350052246603971</v>
+        <v>0.023088051455927398</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B70" t="s">
-        <v>56</v>
+        <v>91</v>
       </c>
       <c r="C70" t="s">
-        <v>133</v>
+        <v>168</v>
       </c>
       <c r="D70" s="1">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="E70" s="1">
-        <v>0.76162790697674421</v>
+        <v>0.978494623655914</v>
       </c>
       <c r="F70" s="1">
         <v>22</v>
       </c>
       <c r="G70" s="1">
-        <v>0.72727272727272729</v>
+        <v>1</v>
       </c>
       <c r="H70" s="1">
-        <v>-0.0343551797040169</v>
+        <v>0.021505376344085999</v>
       </c>
       <c r="I70" s="1">
-        <v>0.60952823223207053</v>
+        <v>0.49205977192767397</v>
       </c>
       <c r="J70" s="1">
-        <v>0.0343551797040169</v>
+        <v>0.021505376344085999</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="C71" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="D71" s="1">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E71" s="1">
-        <v>0.6187458378928048</v>
+        <v>0.74715909090909094</v>
       </c>
       <c r="F71" s="1">
         <v>22</v>
       </c>
       <c r="G71" s="1">
-        <v>0.65224689380689105</v>
+        <v>0.72727272727272729</v>
       </c>
       <c r="H71" s="1">
-        <v>0.033501055914086302</v>
+        <v>-0.019886363636363601</v>
       </c>
       <c r="I71" s="1">
-        <v>0.21233908220317699</v>
+        <v>0.77525265137558042</v>
       </c>
       <c r="J71" s="1">
-        <v>0.033501055914086302</v>
+        <v>0.019886363636363601</v>
       </c>
     </row>
     <row r="72">
@@ -6288,383 +6155,223 @@
         <v>27</v>
       </c>
       <c r="B72" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C72" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D72" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E72" s="1">
-        <v>0.6187458378928048</v>
+        <v>0.1075268817204301</v>
       </c>
       <c r="F72" s="1">
         <v>22</v>
       </c>
       <c r="G72" s="1">
-        <v>0.65224689380689105</v>
+        <v>0.090909090909090898</v>
       </c>
       <c r="H72" s="1">
-        <v>0.033501055914086302</v>
+        <v>-0.016617790811339201</v>
       </c>
       <c r="I72" s="1">
-        <v>0.21233908220317699</v>
+        <v>0.82057849198008404</v>
       </c>
       <c r="J72" s="1">
-        <v>0.033501055914086302</v>
+        <v>0.016617790811339201</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B73" t="s">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="C73" t="s">
-        <v>149</v>
+        <v>183</v>
       </c>
       <c r="D73" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E73" s="1">
-        <v>0.12087912087912089</v>
+        <v>0.84946236559139787</v>
       </c>
       <c r="F73" s="1">
         <v>22</v>
       </c>
       <c r="G73" s="1">
-        <v>0.090909090909090898</v>
+        <v>0.86363636363636365</v>
       </c>
       <c r="H73" s="1">
-        <v>-0.029970029970029999</v>
+        <v>0.0141739980449658</v>
       </c>
       <c r="I73" s="1">
-        <v>0.69572766973562561</v>
+        <v>0.86767335157620629</v>
       </c>
       <c r="J73" s="1">
-        <v>0.029970029970029999</v>
+        <v>0.0141739980449658</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B74" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="C74" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="D74" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E74" s="1">
-        <v>0.51648351648351654</v>
+        <v>0.60394265286384086</v>
       </c>
       <c r="F74" s="1">
         <v>22</v>
       </c>
       <c r="G74" s="1">
-        <v>0.54545454545454541</v>
+        <v>0.61742424016649078</v>
       </c>
       <c r="H74" s="1">
-        <v>0.028971028971028899</v>
+        <v>0.0134815873026499</v>
       </c>
       <c r="I74" s="1">
-        <v>0.80921216276490049</v>
+        <v>0.69693320030264905</v>
       </c>
       <c r="J74" s="1">
-        <v>0.028971028971028899</v>
+        <v>0.0134815873026499</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B75" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="C75" t="s">
-        <v>27</v>
+        <v>151</v>
       </c>
       <c r="D75" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E75" s="1">
-        <v>0.61083811914527808</v>
+        <v>0.40860215053763438</v>
       </c>
       <c r="F75" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G75" s="1">
-        <v>0.6348355656320398</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="H75" s="1">
-        <v>0.023997446486761699</v>
+        <v>0.0080645161290322995</v>
       </c>
       <c r="I75" s="1">
-        <v>0.37017392314130881</v>
+        <v>0.8901728565194712</v>
       </c>
       <c r="J75" s="1">
-        <v>0.023997446486761699</v>
+        <v>0.0080645161290322995</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B76" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="C76" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="D76" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E76" s="1">
-        <v>0.97802197802197799</v>
+        <v>0.31182795698924731</v>
       </c>
       <c r="F76" s="1">
         <v>22</v>
       </c>
       <c r="G76" s="1">
-        <v>1</v>
+        <v>0.31818181818181818</v>
       </c>
       <c r="H76" s="1">
-        <v>0.021978021978022001</v>
+        <v>0.0063538611925708999</v>
       </c>
       <c r="I76" s="1">
-        <v>0.48733919649206342</v>
+        <v>0.95441616004135088</v>
       </c>
       <c r="J76" s="1">
-        <v>0.021978021978022001</v>
+        <v>0.0063538611925708999</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B77" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C77" t="s">
-        <v>183</v>
+        <v>155</v>
       </c>
       <c r="D77" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E77" s="1">
-        <v>0.84615384615384615</v>
+        <v>0.086021505376344107</v>
       </c>
       <c r="F77" s="1">
         <v>22</v>
       </c>
       <c r="G77" s="1">
-        <v>0.86363636363636365</v>
+        <v>0.090909090909090898</v>
       </c>
       <c r="H77" s="1">
-        <v>0.017482517482517501</v>
+        <v>0.0048875855327467996</v>
       </c>
       <c r="I77" s="1">
-        <v>0.83869457181096274</v>
+        <v>0.94231045207869979</v>
       </c>
       <c r="J77" s="1">
-        <v>0.017482517482517501</v>
+        <v>0.0048875855327467996</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B78" t="s">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="C78" t="s">
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="D78" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E78" s="1">
-        <v>0.60293040301773571</v>
+        <v>0.77419354838709675</v>
       </c>
       <c r="F78" s="1">
         <v>22</v>
       </c>
       <c r="G78" s="1">
-        <v>0.61742424016649078</v>
+        <v>0.77272727272727271</v>
       </c>
       <c r="H78" s="1">
-        <v>0.014493837148755099</v>
+        <v>-0.0014662756598240001</v>
       </c>
       <c r="I78" s="1">
-        <v>0.67300812961515244</v>
+        <v>0.9883321736490267</v>
       </c>
       <c r="J78" s="1">
-        <v>0.014493837148755099</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s">
-        <v>27</v>
-      </c>
-      <c r="B79" t="s">
-        <v>73</v>
-      </c>
-      <c r="C79" t="s">
-        <v>150</v>
-      </c>
-      <c r="D79" s="1">
-        <v>91</v>
-      </c>
-      <c r="E79" s="1">
-        <v>0.60293040301773571</v>
-      </c>
-      <c r="F79" s="1">
-        <v>22</v>
-      </c>
-      <c r="G79" s="1">
-        <v>0.61742424016649078</v>
-      </c>
-      <c r="H79" s="1">
-        <v>0.014493837148755099</v>
-      </c>
-      <c r="I79" s="1">
-        <v>0.67300812961515244</v>
-      </c>
-      <c r="J79" s="1">
-        <v>0.014493837148755099</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s">
-        <v>28</v>
-      </c>
-      <c r="B80" t="s">
-        <v>78</v>
-      </c>
-      <c r="C80" t="s">
-        <v>155</v>
-      </c>
-      <c r="D80" s="1">
-        <v>91</v>
-      </c>
-      <c r="E80" s="1">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="F80" s="1">
-        <v>22</v>
-      </c>
-      <c r="G80" s="1">
-        <v>0.090909090909090898</v>
-      </c>
-      <c r="H80" s="1">
-        <v>0.013986013986014</v>
-      </c>
-      <c r="I80" s="1">
-        <v>0.82973704019732786</v>
-      </c>
-      <c r="J80" s="1">
-        <v>0.013986013986014</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s">
-        <v>30</v>
-      </c>
-      <c r="B81" t="s">
-        <v>107</v>
-      </c>
-      <c r="C81" t="s">
-        <v>184</v>
-      </c>
-      <c r="D81" s="1">
-        <v>91</v>
-      </c>
-      <c r="E81" s="1">
-        <v>0.30769230769230771</v>
-      </c>
-      <c r="F81" s="1">
-        <v>22</v>
-      </c>
-      <c r="G81" s="1">
-        <v>0.31818181818181818</v>
-      </c>
-      <c r="H81" s="1">
-        <v>0.0104895104895105</v>
-      </c>
-      <c r="I81" s="1">
-        <v>0.9247696454183334</v>
-      </c>
-      <c r="J81" s="1">
-        <v>0.0104895104895105</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s">
-        <v>27</v>
-      </c>
-      <c r="B82" t="s">
-        <v>74</v>
-      </c>
-      <c r="C82" t="s">
-        <v>151</v>
-      </c>
-      <c r="D82" s="1">
-        <v>91</v>
-      </c>
-      <c r="E82" s="1">
-        <v>0.40659340659340659</v>
-      </c>
-      <c r="F82" s="1">
-        <v>21</v>
-      </c>
-      <c r="G82" s="1">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="H82" s="1">
-        <v>0.0100732600732601</v>
-      </c>
-      <c r="I82" s="1">
-        <v>0.86306942797487096</v>
-      </c>
-      <c r="J82" s="1">
-        <v>0.0100732600732601</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s">
-        <v>30</v>
-      </c>
-      <c r="B83" t="s">
-        <v>108</v>
-      </c>
-      <c r="C83" t="s">
-        <v>185</v>
-      </c>
-      <c r="D83" s="1">
-        <v>91</v>
-      </c>
-      <c r="E83" s="1">
-        <v>0.78021978021978022</v>
-      </c>
-      <c r="F83" s="1">
-        <v>22</v>
-      </c>
-      <c r="G83" s="1">
-        <v>0.77272727272727271</v>
-      </c>
-      <c r="H83" s="1">
-        <v>-0.0074925074925074999</v>
-      </c>
-      <c r="I83" s="1">
-        <v>0.94010805705080525</v>
-      </c>
-      <c r="J83" s="1">
-        <v>0.0074925074925074999</v>
+        <v>0.0014662756598240001</v>
       </c>
     </row>
   </sheetData>
@@ -6673,7 +6380,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6719,10 +6426,10 @@
         <v>169</v>
       </c>
       <c r="D2" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E2" s="1">
-        <v>2.285714285714286</v>
+        <v>2.301075268817204</v>
       </c>
       <c r="F2" s="1">
         <v>22</v>
@@ -6731,13 +6438,13 @@
         <v>1.5909090909090911</v>
       </c>
       <c r="H2" s="1">
-        <v>-0.69480519480519498</v>
+        <v>-0.71016617790811298</v>
       </c>
       <c r="I2" s="1">
-        <v>0.0025864446227961998</v>
+        <v>0.0019609477212618001</v>
       </c>
       <c r="J2" s="1">
-        <v>0.69480519480519498</v>
+        <v>0.71016617790811298</v>
       </c>
     </row>
     <row r="3">
@@ -6751,10 +6458,10 @@
         <v>152</v>
       </c>
       <c r="D3" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E3" s="1">
-        <v>0.2967032967032967</v>
+        <v>0.29032258064516131</v>
       </c>
       <c r="F3" s="1">
         <v>22</v>
@@ -6763,13 +6470,13 @@
         <v>0.77272727272727271</v>
       </c>
       <c r="H3" s="1">
-        <v>0.476023976023976</v>
+        <v>0.4824046920821114</v>
       </c>
       <c r="I3" s="1">
-        <v>2.3469505292300001e-05</v>
+        <v>1.6085554625300001e-05</v>
       </c>
       <c r="J3" s="1">
-        <v>0.476023976023976</v>
+        <v>0.4824046920821114</v>
       </c>
     </row>
     <row r="4">
@@ -6783,10 +6490,10 @@
         <v>170</v>
       </c>
       <c r="D4" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E4" s="1">
-        <v>0.53846153846153844</v>
+        <v>0.55913978494623651</v>
       </c>
       <c r="F4" s="1">
         <v>22</v>
@@ -6795,13 +6502,13 @@
         <v>0.090909090909090898</v>
       </c>
       <c r="H4" s="1">
-        <v>-0.44755244755244761</v>
+        <v>-0.46823069403714562</v>
       </c>
       <c r="I4" s="1">
-        <v>0.00010829431630969999</v>
+        <v>4.94375614732e-05</v>
       </c>
       <c r="J4" s="1">
-        <v>0.44755244755244761</v>
+        <v>0.46823069403714562</v>
       </c>
     </row>
     <row r="5">
@@ -6815,10 +6522,10 @@
         <v>153</v>
       </c>
       <c r="D5" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E5" s="1">
-        <v>0.25274725274725268</v>
+        <v>0.25806451612903231</v>
       </c>
       <c r="F5" s="1">
         <v>22</v>
@@ -6827,13 +6534,13 @@
         <v>0.59090909090909094</v>
       </c>
       <c r="H5" s="1">
-        <v>0.33816183816183831</v>
+        <v>0.33284457478005858</v>
       </c>
       <c r="I5" s="1">
-        <v>0.0020264466138074999</v>
+        <v>0.0024169278216036</v>
       </c>
       <c r="J5" s="1">
-        <v>0.33816183816183831</v>
+        <v>0.33284457478005858</v>
       </c>
     </row>
     <row r="6">
@@ -6847,10 +6554,10 @@
         <v>171</v>
       </c>
       <c r="D6" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E6" s="1">
-        <v>0.75824175824175821</v>
+        <v>0.76344086021505375</v>
       </c>
       <c r="F6" s="1">
         <v>22</v>
@@ -6859,13 +6566,13 @@
         <v>0.45454545454545447</v>
       </c>
       <c r="H6" s="1">
-        <v>-0.30369630369630368</v>
+        <v>-0.30889540566959928</v>
       </c>
       <c r="I6" s="1">
-        <v>0.0050254356935673997</v>
+        <v>0.0040265127730818003</v>
       </c>
       <c r="J6" s="1">
-        <v>0.30369630369630368</v>
+        <v>0.30889540566959928</v>
       </c>
     </row>
     <row r="7">
@@ -6879,10 +6586,10 @@
         <v>154</v>
       </c>
       <c r="D7" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E7" s="1">
-        <v>0.087912087912087905</v>
+        <v>0.096774193548387094</v>
       </c>
       <c r="F7" s="1">
         <v>22</v>
@@ -6891,13 +6598,13 @@
         <v>0.36363636363636359</v>
       </c>
       <c r="H7" s="1">
-        <v>0.27572427572427571</v>
+        <v>0.26686217008797652</v>
       </c>
       <c r="I7" s="1">
-        <v>0.00073214846816179997</v>
+        <v>0.0013326767126349999</v>
       </c>
       <c r="J7" s="1">
-        <v>0.27572427572427571</v>
+        <v>0.26686217008797652</v>
       </c>
     </row>
     <row r="8">
@@ -6911,10 +6618,10 @@
         <v>172</v>
       </c>
       <c r="D8" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E8" s="1">
-        <v>0.68681318681318682</v>
+        <v>0.68817204301075274</v>
       </c>
       <c r="F8" s="1">
         <v>22</v>
@@ -6923,13 +6630,13 @@
         <v>0.93181818181818177</v>
       </c>
       <c r="H8" s="1">
-        <v>0.24500499500499501</v>
+        <v>0.243646138807429</v>
       </c>
       <c r="I8" s="1">
-        <v>0.0037600823987185999</v>
+        <v>0.0037286887679765998</v>
       </c>
       <c r="J8" s="1">
-        <v>0.24500499500499501</v>
+        <v>0.243646138807429</v>
       </c>
     </row>
     <row r="9">
@@ -6943,10 +6650,10 @@
         <v>173</v>
       </c>
       <c r="D9" s="1">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E9" s="1">
-        <v>0.55223880597014929</v>
+        <v>0.55434782608695654</v>
       </c>
       <c r="F9" s="1">
         <v>19</v>
@@ -6955,77 +6662,77 @@
         <v>0.77631578947368418</v>
       </c>
       <c r="H9" s="1">
-        <v>0.22407698350353489</v>
+        <v>0.22196796338672761</v>
       </c>
       <c r="I9" s="1">
-        <v>0.0013517296258888001</v>
+        <v>0.0013141839603253999</v>
       </c>
       <c r="J9" s="1">
-        <v>0.22407698350353489</v>
+        <v>0.22196796338672761</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="C10" t="s">
-        <v>118</v>
+        <v>174</v>
       </c>
       <c r="D10" s="1">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E10" s="1">
-        <v>0.45170454545454553</v>
+        <v>0.5161290322580645</v>
       </c>
       <c r="F10" s="1">
         <v>22</v>
       </c>
       <c r="G10" s="1">
-        <v>0.67045454545454541</v>
+        <v>0.72727272727272729</v>
       </c>
       <c r="H10" s="1">
-        <v>0.21874999999999989</v>
+        <v>0.21114369501466279</v>
       </c>
       <c r="I10" s="1">
-        <v>0.0011524680243634</v>
+        <v>0.074149097587517005</v>
       </c>
       <c r="J10" s="1">
-        <v>0.21874999999999989</v>
+        <v>0.21114369501466279</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B11" t="s">
-        <v>97</v>
+        <v>41</v>
       </c>
       <c r="C11" t="s">
-        <v>174</v>
+        <v>118</v>
       </c>
       <c r="D11" s="1">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E11" s="1">
-        <v>0.51648351648351654</v>
+        <v>0.46111111111111108</v>
       </c>
       <c r="F11" s="1">
         <v>22</v>
       </c>
       <c r="G11" s="1">
-        <v>0.72727272727272729</v>
+        <v>0.67045454545454541</v>
       </c>
       <c r="H11" s="1">
-        <v>0.21078921078921081</v>
+        <v>0.2093434343434343</v>
       </c>
       <c r="I11" s="1">
-        <v>0.075214504306689606</v>
+        <v>0.0018960041074505001</v>
       </c>
       <c r="J11" s="1">
-        <v>0.21078921078921081</v>
+        <v>0.2093434343434343</v>
       </c>
     </row>
     <row r="12">
@@ -7039,10 +6746,10 @@
         <v>175</v>
       </c>
       <c r="D12" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E12" s="1">
-        <v>0.52304385131695763</v>
+        <v>0.52456441365422746</v>
       </c>
       <c r="F12" s="1">
         <v>22</v>
@@ -7051,13 +6758,13 @@
         <v>0.71448863636363635</v>
       </c>
       <c r="H12" s="1">
-        <v>0.19144478504667869</v>
+        <v>0.1899242227094089</v>
       </c>
       <c r="I12" s="1">
-        <v>0.00071198271501949999</v>
+        <v>0.00070536868281790004</v>
       </c>
       <c r="J12" s="1">
-        <v>0.19144478504667869</v>
+        <v>0.1899242227094089</v>
       </c>
     </row>
     <row r="13">
@@ -7065,95 +6772,95 @@
         <v>30</v>
       </c>
       <c r="B13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D13" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E13" s="1">
-        <v>0.52304385131695763</v>
+        <v>0.53763440860215051</v>
       </c>
       <c r="F13" s="1">
         <v>22</v>
       </c>
       <c r="G13" s="1">
-        <v>0.71448863636363635</v>
+        <v>0.72727272727272729</v>
       </c>
       <c r="H13" s="1">
-        <v>0.19144478504667869</v>
+        <v>0.18963831867057679</v>
       </c>
       <c r="I13" s="1">
-        <v>0.00071198271501949999</v>
+        <v>0.1075943763256744</v>
       </c>
       <c r="J13" s="1">
-        <v>0.19144478504667869</v>
+        <v>0.18963831867057679</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>99</v>
+        <v>42</v>
       </c>
       <c r="C14" t="s">
-        <v>176</v>
+        <v>119</v>
       </c>
       <c r="D14" s="1">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E14" s="1">
-        <v>0.53846153846153844</v>
+        <v>0.42222222222222222</v>
       </c>
       <c r="F14" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G14" s="1">
-        <v>0.72727272727272729</v>
+        <v>0.6071428571428571</v>
       </c>
       <c r="H14" s="1">
-        <v>0.18881118881118891</v>
+        <v>0.1849206349206349</v>
       </c>
       <c r="I14" s="1">
-        <v>0.1097985927780615</v>
+        <v>0.0082921406870097008</v>
       </c>
       <c r="J14" s="1">
-        <v>0.18881118881118891</v>
+        <v>0.1849206349206349</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="C15" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="D15" s="1">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E15" s="1">
-        <v>0.42897727272727271</v>
+        <v>0.30107526881720431</v>
       </c>
       <c r="F15" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G15" s="1">
-        <v>0.6071428571428571</v>
+        <v>0.13636363636363641</v>
       </c>
       <c r="H15" s="1">
-        <v>0.17816558441558439</v>
+        <v>-0.1647116324535679</v>
       </c>
       <c r="I15" s="1">
-        <v>0.011995828540544</v>
+        <v>0.11948466631400551</v>
       </c>
       <c r="J15" s="1">
-        <v>0.17816558441558439</v>
+        <v>0.1647116324535679</v>
       </c>
     </row>
     <row r="16">
@@ -7161,191 +6868,191 @@
         <v>27</v>
       </c>
       <c r="B16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D16" s="1">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E16" s="1">
-        <v>0.2967032967032967</v>
+        <v>0.5252808988764045</v>
       </c>
       <c r="F16" s="1">
         <v>22</v>
       </c>
       <c r="G16" s="1">
-        <v>0.13636363636363641</v>
+        <v>0.375</v>
       </c>
       <c r="H16" s="1">
-        <v>-0.16033966033966029</v>
+        <v>-0.1502808988764045</v>
       </c>
       <c r="I16" s="1">
-        <v>0.1287057679630938</v>
+        <v>0.038062927313723197</v>
       </c>
       <c r="J16" s="1">
-        <v>0.16033966033966029</v>
+        <v>0.1502808988764045</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s">
-        <v>59</v>
+        <v>100</v>
       </c>
       <c r="C17" t="s">
-        <v>136</v>
+        <v>177</v>
       </c>
       <c r="D17" s="1">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E17" s="1">
-        <v>0.52011494252873558</v>
+        <v>0.5053763440860215</v>
       </c>
       <c r="F17" s="1">
         <v>22</v>
       </c>
       <c r="G17" s="1">
-        <v>0.375</v>
+        <v>0.63636363636363635</v>
       </c>
       <c r="H17" s="1">
-        <v>-0.14511494252873561</v>
+        <v>0.13098729227761491</v>
       </c>
       <c r="I17" s="1">
-        <v>0.043689650194955701</v>
+        <v>0.27224935160037622</v>
       </c>
       <c r="J17" s="1">
-        <v>0.14511494252873561</v>
+        <v>0.13098729227761491</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="C18" t="s">
-        <v>110</v>
+        <v>137</v>
       </c>
       <c r="D18" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E18" s="1">
-        <v>0.67648417707327957</v>
+        <v>0.59677419354838712</v>
       </c>
       <c r="F18" s="1">
         <v>22</v>
       </c>
       <c r="G18" s="1">
-        <v>0.80842424793676892</v>
+        <v>0.72727272727272729</v>
       </c>
       <c r="H18" s="1">
-        <v>0.13194007086348941</v>
+        <v>0.1304985337243402</v>
       </c>
       <c r="I18" s="1">
-        <v>1.51330004656e-05</v>
+        <v>0.010965617038097701</v>
       </c>
       <c r="J18" s="1">
-        <v>0.13194007086348941</v>
+        <v>0.1304985337243402</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="C19" t="s">
-        <v>137</v>
+        <v>110</v>
       </c>
       <c r="D19" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E19" s="1">
-        <v>0.59615384615384615</v>
+        <v>0.67828619063541451</v>
       </c>
       <c r="F19" s="1">
         <v>22</v>
       </c>
       <c r="G19" s="1">
-        <v>0.72727272727272729</v>
+        <v>0.80842424793676892</v>
       </c>
       <c r="H19" s="1">
-        <v>0.13111888111888109</v>
+        <v>0.13013805730135439</v>
       </c>
       <c r="I19" s="1">
-        <v>0.0112288864446566</v>
+        <v>1.9104368201999999e-05</v>
       </c>
       <c r="J19" s="1">
-        <v>0.13111888111888109</v>
+        <v>0.13013805730135439</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="C20" t="s">
-        <v>177</v>
+        <v>113</v>
       </c>
       <c r="D20" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E20" s="1">
-        <v>0.50549450549450547</v>
+        <v>0.76238479569394102</v>
       </c>
       <c r="F20" s="1">
         <v>22</v>
       </c>
       <c r="G20" s="1">
-        <v>0.63636363636363635</v>
+        <v>0.89157197421247314</v>
       </c>
       <c r="H20" s="1">
-        <v>0.13086913086913091</v>
+        <v>0.12918717851853209</v>
       </c>
       <c r="I20" s="1">
-        <v>0.27373558683540788</v>
+        <v>0.00024086750106500001</v>
       </c>
       <c r="J20" s="1">
-        <v>0.13086913086913091</v>
+        <v>0.12918717851853209</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C21" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="D21" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E21" s="1">
-        <v>0.76128336263226937</v>
+        <v>0.83870967741935487</v>
       </c>
       <c r="F21" s="1">
         <v>22</v>
       </c>
       <c r="G21" s="1">
-        <v>0.89157197421247314</v>
+        <v>0.95454545454545459</v>
       </c>
       <c r="H21" s="1">
-        <v>0.1302886115802038</v>
+        <v>0.1158357771260997</v>
       </c>
       <c r="I21" s="1">
-        <v>0.00020955452112240001</v>
+        <v>0.1607752812799218</v>
       </c>
       <c r="J21" s="1">
-        <v>0.1302886115802038</v>
+        <v>0.1158357771260997</v>
       </c>
     </row>
     <row r="22">
@@ -7353,31 +7060,31 @@
         <v>26</v>
       </c>
       <c r="B22" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C22" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D22" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E22" s="1">
-        <v>0.8351648351648352</v>
+        <v>0.43010752688172038</v>
       </c>
       <c r="F22" s="1">
         <v>22</v>
       </c>
       <c r="G22" s="1">
-        <v>0.95454545454545459</v>
+        <v>0.54545454545454541</v>
       </c>
       <c r="H22" s="1">
-        <v>0.1193806193806194</v>
+        <v>0.11534701857282501</v>
       </c>
       <c r="I22" s="1">
-        <v>0.15216897342503741</v>
+        <v>0.3326032191300492</v>
       </c>
       <c r="J22" s="1">
-        <v>0.1193806193806194</v>
+        <v>0.11534701857282501</v>
       </c>
     </row>
     <row r="23">
@@ -7391,10 +7098,10 @@
         <v>178</v>
       </c>
       <c r="D23" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E23" s="1">
-        <v>0.52747252747252749</v>
+        <v>0.5268817204301075</v>
       </c>
       <c r="F23" s="1">
         <v>22</v>
@@ -7403,13 +7110,13 @@
         <v>0.63636363636363635</v>
       </c>
       <c r="H23" s="1">
-        <v>0.1088911088911089</v>
+        <v>0.10948191593352891</v>
       </c>
       <c r="I23" s="1">
-        <v>0.36149197990439819</v>
+        <v>0.35787189970000383</v>
       </c>
       <c r="J23" s="1">
-        <v>0.1088911088911089</v>
+        <v>0.10948191593352891</v>
       </c>
     </row>
     <row r="24">
@@ -7423,10 +7130,10 @@
         <v>179</v>
       </c>
       <c r="D24" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E24" s="1">
-        <v>0.54990843003922763</v>
+        <v>0.54973118808320776</v>
       </c>
       <c r="F24" s="1">
         <v>22</v>
@@ -7435,13 +7142,13 @@
         <v>0.6549873846498403</v>
       </c>
       <c r="H24" s="1">
-        <v>0.1050789546106127</v>
+        <v>0.1052561965666325</v>
       </c>
       <c r="I24" s="1">
-        <v>0.21430643662257179</v>
+        <v>0.21503700877172391</v>
       </c>
       <c r="J24" s="1">
-        <v>0.1050789546106127</v>
+        <v>0.1052561965666325</v>
       </c>
     </row>
     <row r="25">
@@ -7455,10 +7162,10 @@
         <v>114</v>
       </c>
       <c r="D25" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E25" s="1">
-        <v>0.65477272647095253</v>
+        <v>0.65486559055505256</v>
       </c>
       <c r="F25" s="1">
         <v>22</v>
@@ -7467,141 +7174,141 @@
         <v>0.75867769257588824</v>
       </c>
       <c r="H25" s="1">
-        <v>0.1039049661049357</v>
+        <v>0.1038121020208357</v>
       </c>
       <c r="I25" s="1">
-        <v>0.023254832145028301</v>
+        <v>0.022014726228919299</v>
       </c>
       <c r="J25" s="1">
-        <v>0.1039049661049357</v>
+        <v>0.1038121020208357</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B26" t="s">
-        <v>61</v>
+        <v>103</v>
       </c>
       <c r="C26" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="D26" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E26" s="1">
-        <v>0.59340659340659341</v>
+        <v>0.53763440860215051</v>
       </c>
       <c r="F26" s="1">
         <v>22</v>
       </c>
       <c r="G26" s="1">
-        <v>0.69318181818181823</v>
+        <v>0.63636363636363635</v>
       </c>
       <c r="H26" s="1">
-        <v>0.099775224775224797</v>
+        <v>0.098729227761485794</v>
       </c>
       <c r="I26" s="1">
-        <v>0.057697490578584601</v>
+        <v>0.40633414267841389</v>
       </c>
       <c r="J26" s="1">
-        <v>0.099775224775224797</v>
+        <v>0.098729227761485794</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>103</v>
+        <v>61</v>
       </c>
       <c r="C27" t="s">
-        <v>180</v>
+        <v>138</v>
       </c>
       <c r="D27" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E27" s="1">
-        <v>0.53846153846153844</v>
+        <v>0.59677419354838712</v>
       </c>
       <c r="F27" s="1">
         <v>22</v>
       </c>
       <c r="G27" s="1">
-        <v>0.63636363636363635</v>
+        <v>0.69318181818181823</v>
       </c>
       <c r="H27" s="1">
-        <v>0.097902097902097904</v>
+        <v>0.096407624633431097</v>
       </c>
       <c r="I27" s="1">
-        <v>0.41124505860639249</v>
+        <v>0.064734462072081403</v>
       </c>
       <c r="J27" s="1">
-        <v>0.097902097902097904</v>
+        <v>0.096407624633431097</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="C28" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="D28" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E28" s="1">
-        <v>0.45054945054945062</v>
+        <v>0.086021505376344107</v>
       </c>
       <c r="F28" s="1">
         <v>22</v>
       </c>
       <c r="G28" s="1">
-        <v>0.54545454545454541</v>
+        <v>0</v>
       </c>
       <c r="H28" s="1">
-        <v>0.0949050949050948</v>
+        <v>-0.086021505376344107</v>
       </c>
       <c r="I28" s="1">
-        <v>0.4279525320297285</v>
+        <v>0.15651386444400159</v>
       </c>
       <c r="J28" s="1">
-        <v>0.0949050949050948</v>
+        <v>0.086021505376344107</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="C29" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="D29" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E29" s="1">
-        <v>0.087912087912087905</v>
+        <v>0.68817204301075274</v>
       </c>
       <c r="F29" s="1">
         <v>22</v>
       </c>
       <c r="G29" s="1">
-        <v>0</v>
+        <v>0.77272727272727271</v>
       </c>
       <c r="H29" s="1">
-        <v>-0.087912087912087905</v>
+        <v>0.084555229716520006</v>
       </c>
       <c r="I29" s="1">
-        <v>0.1517681784726721</v>
+        <v>0.43890215547745593</v>
       </c>
       <c r="J29" s="1">
-        <v>0.087912087912087905</v>
+        <v>0.084555229716520006</v>
       </c>
     </row>
     <row r="30">
@@ -7609,16 +7316,16 @@
         <v>26</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C30" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D30" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E30" s="1">
-        <v>0.61510880062213313</v>
+        <v>0.615209507205153</v>
       </c>
       <c r="F30" s="1">
         <v>22</v>
@@ -7627,45 +7334,45 @@
         <v>0.69829996065659961</v>
       </c>
       <c r="H30" s="1">
-        <v>0.083191160034466499</v>
+        <v>0.083090453451446597</v>
       </c>
       <c r="I30" s="1">
-        <v>0.025535190366513801</v>
+        <v>0.023705043506038501</v>
       </c>
       <c r="J30" s="1">
-        <v>0.083191160034466499</v>
+        <v>0.083090453451446597</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="C31" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="D31" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E31" s="1">
-        <v>0.61510880062213313</v>
+        <v>0.61021505376344087</v>
       </c>
       <c r="F31" s="1">
         <v>22</v>
       </c>
       <c r="G31" s="1">
-        <v>0.69829996065659961</v>
+        <v>0.69318181818181823</v>
       </c>
       <c r="H31" s="1">
-        <v>0.083191160034466499</v>
+        <v>0.082966764418377401</v>
       </c>
       <c r="I31" s="1">
-        <v>0.025535190366513801</v>
+        <v>0.11299979230854509</v>
       </c>
       <c r="J31" s="1">
-        <v>0.083191160034466499</v>
+        <v>0.082966764418377401</v>
       </c>
     </row>
     <row r="32">
@@ -7673,223 +7380,223 @@
         <v>27</v>
       </c>
       <c r="B32" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C32" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D32" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E32" s="1">
-        <v>0.61263736263736268</v>
+        <v>0.59946236559139787</v>
       </c>
       <c r="F32" s="1">
         <v>22</v>
       </c>
       <c r="G32" s="1">
-        <v>0.69318181818181823</v>
+        <v>0.68181818181818177</v>
       </c>
       <c r="H32" s="1">
-        <v>0.080544455544455607</v>
+        <v>0.082355816226783896</v>
       </c>
       <c r="I32" s="1">
-        <v>0.12273202904129769</v>
+        <v>0.081563711558646695</v>
       </c>
       <c r="J32" s="1">
-        <v>0.080544455544455607</v>
+        <v>0.082355816226783896</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B33" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="C33" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="D33" s="1">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E33" s="1">
-        <v>0.69230769230769229</v>
+        <v>0.6713483146067416</v>
       </c>
       <c r="F33" s="1">
         <v>22</v>
       </c>
       <c r="G33" s="1">
-        <v>0.77272727272727271</v>
+        <v>0.75</v>
       </c>
       <c r="H33" s="1">
-        <v>0.080419580419580403</v>
+        <v>0.078651685393258397</v>
       </c>
       <c r="I33" s="1">
-        <v>0.46107928367593493</v>
+        <v>0.17307573740344351</v>
       </c>
       <c r="J33" s="1">
-        <v>0.080419580419580403</v>
+        <v>0.078651685393258397</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="C34" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="D34" s="1">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="E34" s="1">
-        <v>0.60164835164835162</v>
+        <v>0.6875</v>
       </c>
       <c r="F34" s="1">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G34" s="1">
-        <v>0.68181818181818177</v>
+        <v>0.76470588235294113</v>
       </c>
       <c r="H34" s="1">
-        <v>0.080169830169830106</v>
+        <v>0.077205882352941096</v>
       </c>
       <c r="I34" s="1">
-        <v>0.088129803214070601</v>
+        <v>0.49698882369010422</v>
       </c>
       <c r="J34" s="1">
-        <v>0.080169830169830106</v>
+        <v>0.077205882352941096</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B35" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C35" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D35" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E35" s="1">
-        <v>0.60798011621931092</v>
+        <v>0.64271773253717734</v>
       </c>
       <c r="F35" s="1">
         <v>22</v>
       </c>
       <c r="G35" s="1">
-        <v>0.68582250719720672</v>
+        <v>0.71757883917201648</v>
       </c>
       <c r="H35" s="1">
-        <v>0.077842390977895804</v>
+        <v>0.074861106634839095</v>
       </c>
       <c r="I35" s="1">
-        <v>0.022874150237429801</v>
+        <v>0.00054342656699579999</v>
       </c>
       <c r="J35" s="1">
-        <v>0.077842390977895804</v>
+        <v>0.074861106634839095</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B36" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="C36" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="D36" s="1">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E36" s="1">
-        <v>0.67241379310344829</v>
+        <v>0.4838709677419355</v>
       </c>
       <c r="F36" s="1">
         <v>22</v>
       </c>
       <c r="G36" s="1">
-        <v>0.75</v>
+        <v>0.40909090909090912</v>
       </c>
       <c r="H36" s="1">
-        <v>0.077586206896551699</v>
+        <v>-0.074780058651026396</v>
       </c>
       <c r="I36" s="1">
-        <v>0.17839943572998729</v>
+        <v>0.53154290901188228</v>
       </c>
       <c r="J36" s="1">
-        <v>0.077586206896551699</v>
+        <v>0.074780058651026396</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B37" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="C37" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="D37" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E37" s="1">
-        <v>0.58241758241758246</v>
+        <v>0.61169994950935402</v>
       </c>
       <c r="F37" s="1">
         <v>22</v>
       </c>
       <c r="G37" s="1">
-        <v>0.65909090909090906</v>
+        <v>0.68582250719720672</v>
       </c>
       <c r="H37" s="1">
-        <v>0.076673326673326603</v>
+        <v>0.074122557687852697</v>
       </c>
       <c r="I37" s="1">
-        <v>0.14808856021965239</v>
+        <v>0.029959187331934801</v>
       </c>
       <c r="J37" s="1">
-        <v>0.076673326673326603</v>
+        <v>0.074122557687852697</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B38" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="C38" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="D38" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E38" s="1">
-        <v>0.6410022639966273</v>
+        <v>0.58602150537634412</v>
       </c>
       <c r="F38" s="1">
         <v>22</v>
       </c>
       <c r="G38" s="1">
-        <v>0.71757883917201648</v>
+        <v>0.65909090909090906</v>
       </c>
       <c r="H38" s="1">
-        <v>0.076576575175389197</v>
+        <v>0.073069403714564898</v>
       </c>
       <c r="I38" s="1">
-        <v>0.00037670378643190001</v>
+        <v>0.16534088350526069</v>
       </c>
       <c r="J38" s="1">
-        <v>0.076576575175389197</v>
+        <v>0.073069403714564898</v>
       </c>
     </row>
     <row r="39">
@@ -7897,16 +7604,16 @@
         <v>26</v>
       </c>
       <c r="B39" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C39" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D39" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E39" s="1">
-        <v>0.87912087912087911</v>
+        <v>0.88172043010752688</v>
       </c>
       <c r="F39" s="1">
         <v>22</v>
@@ -7915,45 +7622,45 @@
         <v>0.95454545454545459</v>
       </c>
       <c r="H39" s="1">
-        <v>0.075424575424575493</v>
+        <v>0.072825024437927696</v>
       </c>
       <c r="I39" s="1">
-        <v>0.30705810298076669</v>
+        <v>0.31924939276812558</v>
       </c>
       <c r="J39" s="1">
-        <v>0.075424575424575493</v>
+        <v>0.072825024437927696</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B40" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="C40" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="D40" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E40" s="1">
-        <v>0.48351648351648352</v>
+        <v>0.66913728143579221</v>
       </c>
       <c r="F40" s="1">
         <v>22</v>
       </c>
       <c r="G40" s="1">
-        <v>0.40909090909090912</v>
+        <v>0.74123304946856061</v>
       </c>
       <c r="H40" s="1">
-        <v>-0.074425574425574403</v>
+        <v>0.072095768032768404</v>
       </c>
       <c r="I40" s="1">
-        <v>0.53440024041636403</v>
+        <v>0.015769077113338699</v>
       </c>
       <c r="J40" s="1">
-        <v>0.074425574425574403</v>
+        <v>0.072095768032768404</v>
       </c>
     </row>
     <row r="41">
@@ -7967,10 +7674,10 @@
         <v>116</v>
       </c>
       <c r="D41" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E41" s="1">
-        <v>0.74512531829404305</v>
+        <v>0.7479093616367668</v>
       </c>
       <c r="F41" s="1">
         <v>22</v>
@@ -7979,237 +7686,237 @@
         <v>0.81921211697838525</v>
       </c>
       <c r="H41" s="1">
-        <v>0.074086798684342203</v>
+        <v>0.071302755341618507</v>
       </c>
       <c r="I41" s="1">
-        <v>0.0142565558822026</v>
+        <v>0.019539672517746899</v>
       </c>
       <c r="J41" s="1">
-        <v>0.074086798684342203</v>
+        <v>0.071302755341618507</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B42" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="C42" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="D42" s="1">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="E42" s="1">
-        <v>0.69090909090909092</v>
+        <v>0.59139784946236562</v>
       </c>
       <c r="F42" s="1">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G42" s="1">
-        <v>0.76470588235294113</v>
+        <v>0.65909090909090906</v>
       </c>
       <c r="H42" s="1">
-        <v>0.073796791443850193</v>
+        <v>0.067693059628543398</v>
       </c>
       <c r="I42" s="1">
-        <v>0.51936252607505184</v>
+        <v>0.19989848015592829</v>
       </c>
       <c r="J42" s="1">
-        <v>0.073796791443850193</v>
+        <v>0.067693059628543398</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B43" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C43" t="s">
-        <v>112</v>
+        <v>144</v>
       </c>
       <c r="D43" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E43" s="1">
-        <v>0.66870664927985646</v>
+        <v>0.7553763440860215</v>
       </c>
       <c r="F43" s="1">
         <v>22</v>
       </c>
       <c r="G43" s="1">
-        <v>0.74123304946856061</v>
+        <v>0.81818181818181823</v>
       </c>
       <c r="H43" s="1">
-        <v>0.072526400188704196</v>
+        <v>0.062805474095796704</v>
       </c>
       <c r="I43" s="1">
-        <v>0.015245241111370799</v>
+        <v>0.1006874707948905</v>
       </c>
       <c r="J43" s="1">
-        <v>0.072526400188704196</v>
+        <v>0.062805474095796704</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B44" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="C44" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="D44" s="1">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="E44" s="1">
-        <v>0.58791208791208793</v>
+        <v>0.71818181818181814</v>
       </c>
       <c r="F44" s="1">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G44" s="1">
-        <v>0.65909090909090906</v>
+        <v>0.65625</v>
       </c>
       <c r="H44" s="1">
-        <v>0.0711788211788211</v>
+        <v>-0.061931818181818102</v>
       </c>
       <c r="I44" s="1">
-        <v>0.18066817888897849</v>
+        <v>0.59880668484187516</v>
       </c>
       <c r="J44" s="1">
-        <v>0.0711788211788211</v>
+        <v>0.061931818181818102</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B45" t="s">
-        <v>51</v>
+        <v>104</v>
       </c>
       <c r="C45" t="s">
-        <v>128</v>
+        <v>181</v>
       </c>
       <c r="D45" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E45" s="1">
-        <v>0.2087912087912088</v>
+        <v>0.69959678268560799</v>
       </c>
       <c r="F45" s="1">
         <v>22</v>
       </c>
       <c r="G45" s="1">
-        <v>0.27272727272727271</v>
+        <v>0.75931188193234533</v>
       </c>
       <c r="H45" s="1">
-        <v>0.063936063936063894</v>
+        <v>0.059715099246737298</v>
       </c>
       <c r="I45" s="1">
-        <v>0.52104617563932409</v>
+        <v>0.25757373456635108</v>
       </c>
       <c r="J45" s="1">
-        <v>0.063936063936063894</v>
+        <v>0.059715099246737298</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B46" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="C46" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="D46" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E46" s="1">
-        <v>0.75549450549450547</v>
+        <v>0.21505376344086019</v>
       </c>
       <c r="F46" s="1">
         <v>22</v>
       </c>
       <c r="G46" s="1">
-        <v>0.81818181818181823</v>
+        <v>0.27272727272727271</v>
       </c>
       <c r="H46" s="1">
-        <v>0.062687312687312799</v>
+        <v>0.057673509286412503</v>
       </c>
       <c r="I46" s="1">
-        <v>0.097676700796505006</v>
+        <v>0.56486310795380701</v>
       </c>
       <c r="J46" s="1">
-        <v>0.062687312687312799</v>
+        <v>0.057673509286412503</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B47" t="s">
-        <v>104</v>
+        <v>53</v>
       </c>
       <c r="C47" t="s">
-        <v>181</v>
+        <v>130</v>
       </c>
       <c r="D47" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E47" s="1">
-        <v>0.69803114464649785</v>
+        <v>0.59408602150537637</v>
       </c>
       <c r="F47" s="1">
         <v>22</v>
       </c>
       <c r="G47" s="1">
-        <v>0.75931188193234533</v>
+        <v>0.64772727272727271</v>
       </c>
       <c r="H47" s="1">
-        <v>0.0612807372858475</v>
+        <v>0.053641251221896301</v>
       </c>
       <c r="I47" s="1">
-        <v>0.24579374673905729</v>
+        <v>0.28780031279951213</v>
       </c>
       <c r="J47" s="1">
-        <v>0.0612807372858475</v>
+        <v>0.053641251221896301</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B48" t="s">
-        <v>104</v>
+        <v>68</v>
       </c>
       <c r="C48" t="s">
-        <v>181</v>
+        <v>145</v>
       </c>
       <c r="D48" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E48" s="1">
-        <v>0.69803114464649785</v>
+        <v>0.45161290322580638</v>
       </c>
       <c r="F48" s="1">
         <v>22</v>
       </c>
       <c r="G48" s="1">
-        <v>0.75931188193234533</v>
+        <v>0.5</v>
       </c>
       <c r="H48" s="1">
-        <v>0.0612807372858475</v>
+        <v>0.048387096774193603</v>
       </c>
       <c r="I48" s="1">
-        <v>0.24579374673905729</v>
+        <v>0.68538806215625137</v>
       </c>
       <c r="J48" s="1">
-        <v>0.0612807372858475</v>
+        <v>0.048387096774193603</v>
       </c>
     </row>
     <row r="49">
@@ -8217,287 +7924,287 @@
         <v>26</v>
       </c>
       <c r="B49" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C49" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D49" s="1">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="E49" s="1">
-        <v>0.71698113207547165</v>
+        <v>0.702247191011236</v>
       </c>
       <c r="F49" s="1">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G49" s="1">
-        <v>0.65625</v>
+        <v>0.75</v>
       </c>
       <c r="H49" s="1">
-        <v>-0.060731132075471601</v>
+        <v>0.047752808988764002</v>
       </c>
       <c r="I49" s="1">
-        <v>0.61077787700083586</v>
+        <v>0.51920550288726419</v>
       </c>
       <c r="J49" s="1">
-        <v>0.060731132075471601</v>
+        <v>0.047752808988764002</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B50" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="C50" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="D50" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E50" s="1">
-        <v>0.59340659340659341</v>
+        <v>0.043010752688171998</v>
       </c>
       <c r="F50" s="1">
         <v>22</v>
       </c>
       <c r="G50" s="1">
-        <v>0.64772727272727271</v>
+        <v>0</v>
       </c>
       <c r="H50" s="1">
-        <v>0.054320679320679299</v>
+        <v>-0.043010752688171998</v>
       </c>
       <c r="I50" s="1">
-        <v>0.28551869536860558</v>
+        <v>0.32639522542870719</v>
       </c>
       <c r="J50" s="1">
-        <v>0.054320679320679299</v>
+        <v>0.043010752688171998</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B51" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="C51" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="D51" s="1">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E51" s="1">
-        <v>0.69827586206896552</v>
+        <v>0.70687724249337314</v>
       </c>
       <c r="F51" s="1">
         <v>22</v>
       </c>
       <c r="G51" s="1">
-        <v>0.75</v>
+        <v>0.7486426803198728</v>
       </c>
       <c r="H51" s="1">
-        <v>0.051724137931034503</v>
+        <v>0.041765437826499698</v>
       </c>
       <c r="I51" s="1">
-        <v>0.48825865975192989</v>
+        <v>0.19719782960896681</v>
       </c>
       <c r="J51" s="1">
-        <v>0.051724137931034503</v>
+        <v>0.041765437826499698</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B52" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="C52" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="D52" s="1">
         <v>91</v>
       </c>
       <c r="E52" s="1">
-        <v>0.45054945054945062</v>
+        <v>0.74725274725274726</v>
       </c>
       <c r="F52" s="1">
         <v>22</v>
       </c>
       <c r="G52" s="1">
-        <v>0.5</v>
+        <v>0.78409090909090906</v>
       </c>
       <c r="H52" s="1">
-        <v>0.0494505494505494</v>
+        <v>0.036838161838161798</v>
       </c>
       <c r="I52" s="1">
-        <v>0.67951067214355387</v>
+        <v>0.59172546051504582</v>
       </c>
       <c r="J52" s="1">
-        <v>0.0494505494505494</v>
+        <v>0.036838161838161798</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B53" t="s">
-        <v>69</v>
+        <v>105</v>
       </c>
       <c r="C53" t="s">
-        <v>146</v>
+        <v>182</v>
       </c>
       <c r="D53" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E53" s="1">
-        <v>0.043956043956044001</v>
+        <v>0.31989247311827962</v>
       </c>
       <c r="F53" s="1">
         <v>22</v>
       </c>
       <c r="G53" s="1">
-        <v>0</v>
+        <v>0.35606060606060602</v>
       </c>
       <c r="H53" s="1">
-        <v>-0.043956043956044001</v>
+        <v>0.036168132942326403</v>
       </c>
       <c r="I53" s="1">
-        <v>0.32103413173416762</v>
+        <v>0.50804299508562245</v>
       </c>
       <c r="J53" s="1">
-        <v>0.043956043956044001</v>
+        <v>0.036168132942326403</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B54" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="C54" t="s">
-        <v>117</v>
+        <v>147</v>
       </c>
       <c r="D54" s="1">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E54" s="1">
-        <v>0.70691392185923818</v>
+        <v>0.6713483146067416</v>
       </c>
       <c r="F54" s="1">
         <v>22</v>
       </c>
       <c r="G54" s="1">
-        <v>0.7486426803198728</v>
+        <v>0.70454545454545459</v>
       </c>
       <c r="H54" s="1">
-        <v>0.041728758460634598</v>
+        <v>0.033197139938712997</v>
       </c>
       <c r="I54" s="1">
-        <v>0.19143151962259569</v>
+        <v>0.5585600308312344</v>
       </c>
       <c r="J54" s="1">
-        <v>0.041728758460634598</v>
+        <v>0.033197139938712997</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B55" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="C55" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="D55" s="1">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E55" s="1">
-        <v>0.7443820224719101</v>
+        <v>0.61955237837247956</v>
       </c>
       <c r="F55" s="1">
         <v>22</v>
       </c>
       <c r="G55" s="1">
-        <v>0.78409090909090906</v>
+        <v>0.65224689380689105</v>
       </c>
       <c r="H55" s="1">
-        <v>0.039708886618998997</v>
+        <v>0.0326945154344115</v>
       </c>
       <c r="I55" s="1">
-        <v>0.56625226823520469</v>
+        <v>0.2240407417593582</v>
       </c>
       <c r="J55" s="1">
-        <v>0.039708886618998997</v>
+        <v>0.0326945154344115</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B56" t="s">
-        <v>105</v>
+        <v>56</v>
       </c>
       <c r="C56" t="s">
-        <v>182</v>
+        <v>133</v>
       </c>
       <c r="D56" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E56" s="1">
-        <v>0.3177655677655678</v>
+        <v>0.5161290322580645</v>
       </c>
       <c r="F56" s="1">
         <v>22</v>
       </c>
       <c r="G56" s="1">
-        <v>0.35606060606060602</v>
+        <v>0.54545454545454541</v>
       </c>
       <c r="H56" s="1">
-        <v>0.038295038295038199</v>
+        <v>0.029325513196480898</v>
       </c>
       <c r="I56" s="1">
-        <v>0.47928736223762791</v>
+        <v>0.8064949829553979</v>
       </c>
       <c r="J56" s="1">
-        <v>0.038295038295038199</v>
+        <v>0.029325513196480898</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
+        <v>24</v>
+      </c>
+      <c r="B57" t="s">
+        <v>35</v>
+      </c>
+      <c r="C57" t="s">
         <v>27</v>
       </c>
-      <c r="B57" t="s">
-        <v>70</v>
-      </c>
-      <c r="C57" t="s">
-        <v>147</v>
-      </c>
       <c r="D57" s="1">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E57" s="1">
-        <v>0.66954022988505746</v>
+        <v>0.61174751417611239</v>
       </c>
       <c r="F57" s="1">
         <v>22</v>
       </c>
       <c r="G57" s="1">
-        <v>0.70454545454545459</v>
+        <v>0.6348355656320398</v>
       </c>
       <c r="H57" s="1">
-        <v>0.0350052246603971</v>
+        <v>0.023088051455927398</v>
       </c>
       <c r="I57" s="1">
-        <v>0.53748817890029621</v>
+        <v>0.39299283822349318</v>
       </c>
       <c r="J57" s="1">
-        <v>0.0350052246603971</v>
+        <v>0.023088051455927398</v>
       </c>
     </row>
     <row r="58">
@@ -8505,16 +8212,16 @@
         <v>26</v>
       </c>
       <c r="B58" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C58" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D58" s="1">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E58" s="1">
-        <v>0.76162790697674421</v>
+        <v>0.74715909090909094</v>
       </c>
       <c r="F58" s="1">
         <v>22</v>
@@ -8523,13 +8230,13 @@
         <v>0.72727272727272729</v>
       </c>
       <c r="H58" s="1">
-        <v>-0.0343551797040169</v>
+        <v>-0.019886363636363601</v>
       </c>
       <c r="I58" s="1">
-        <v>0.60952823223207053</v>
+        <v>0.77525265137558042</v>
       </c>
       <c r="J58" s="1">
-        <v>0.0343551797040169</v>
+        <v>0.019886363636363601</v>
       </c>
     </row>
     <row r="59">
@@ -8537,63 +8244,63 @@
         <v>27</v>
       </c>
       <c r="B59" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C59" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D59" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E59" s="1">
-        <v>0.6187458378928048</v>
+        <v>0.1075268817204301</v>
       </c>
       <c r="F59" s="1">
         <v>22</v>
       </c>
       <c r="G59" s="1">
-        <v>0.65224689380689105</v>
+        <v>0.090909090909090898</v>
       </c>
       <c r="H59" s="1">
-        <v>0.033501055914086302</v>
+        <v>-0.016617790811339201</v>
       </c>
       <c r="I59" s="1">
-        <v>0.21233908220317699</v>
+        <v>0.82057849198008404</v>
       </c>
       <c r="J59" s="1">
-        <v>0.033501055914086302</v>
+        <v>0.016617790811339201</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B60" t="s">
-        <v>71</v>
+        <v>106</v>
       </c>
       <c r="C60" t="s">
-        <v>148</v>
+        <v>183</v>
       </c>
       <c r="D60" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E60" s="1">
-        <v>0.6187458378928048</v>
+        <v>0.84946236559139787</v>
       </c>
       <c r="F60" s="1">
         <v>22</v>
       </c>
       <c r="G60" s="1">
-        <v>0.65224689380689105</v>
+        <v>0.86363636363636365</v>
       </c>
       <c r="H60" s="1">
-        <v>0.033501055914086302</v>
+        <v>0.0141739980449658</v>
       </c>
       <c r="I60" s="1">
-        <v>0.21233908220317699</v>
+        <v>0.86767335157620629</v>
       </c>
       <c r="J60" s="1">
-        <v>0.033501055914086302</v>
+        <v>0.0141739980449658</v>
       </c>
     </row>
     <row r="61">
@@ -8601,319 +8308,159 @@
         <v>27</v>
       </c>
       <c r="B61" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C61" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D61" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E61" s="1">
-        <v>0.12087912087912089</v>
+        <v>0.60394265286384086</v>
       </c>
       <c r="F61" s="1">
         <v>22</v>
       </c>
       <c r="G61" s="1">
-        <v>0.090909090909090898</v>
+        <v>0.61742424016649078</v>
       </c>
       <c r="H61" s="1">
-        <v>-0.029970029970029999</v>
+        <v>0.0134815873026499</v>
       </c>
       <c r="I61" s="1">
-        <v>0.69572766973562561</v>
+        <v>0.69693320030264905</v>
       </c>
       <c r="J61" s="1">
-        <v>0.029970029970029999</v>
+        <v>0.0134815873026499</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B62" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="C62" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="D62" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E62" s="1">
-        <v>0.51648351648351654</v>
+        <v>0.40860215053763438</v>
       </c>
       <c r="F62" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G62" s="1">
-        <v>0.54545454545454541</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="H62" s="1">
-        <v>0.028971028971028899</v>
+        <v>0.0080645161290322995</v>
       </c>
       <c r="I62" s="1">
-        <v>0.80921216276490049</v>
+        <v>0.8901728565194712</v>
       </c>
       <c r="J62" s="1">
-        <v>0.028971028971028899</v>
+        <v>0.0080645161290322995</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B63" t="s">
-        <v>35</v>
+        <v>107</v>
       </c>
       <c r="C63" t="s">
-        <v>27</v>
+        <v>184</v>
       </c>
       <c r="D63" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E63" s="1">
-        <v>0.61083811914527808</v>
+        <v>0.31182795698924731</v>
       </c>
       <c r="F63" s="1">
         <v>22</v>
       </c>
       <c r="G63" s="1">
-        <v>0.6348355656320398</v>
+        <v>0.31818181818181818</v>
       </c>
       <c r="H63" s="1">
-        <v>0.023997446486761699</v>
+        <v>0.0063538611925708999</v>
       </c>
       <c r="I63" s="1">
-        <v>0.37017392314130881</v>
+        <v>0.95441616004135088</v>
       </c>
       <c r="J63" s="1">
-        <v>0.023997446486761699</v>
+        <v>0.0063538611925708999</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B64" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C64" t="s">
-        <v>183</v>
+        <v>155</v>
       </c>
       <c r="D64" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E64" s="1">
-        <v>0.84615384615384615</v>
+        <v>0.086021505376344107</v>
       </c>
       <c r="F64" s="1">
         <v>22</v>
       </c>
       <c r="G64" s="1">
-        <v>0.86363636363636365</v>
+        <v>0.090909090909090898</v>
       </c>
       <c r="H64" s="1">
-        <v>0.017482517482517501</v>
+        <v>0.0048875855327467996</v>
       </c>
       <c r="I64" s="1">
-        <v>0.83869457181096274</v>
+        <v>0.94231045207869979</v>
       </c>
       <c r="J64" s="1">
-        <v>0.017482517482517501</v>
+        <v>0.0048875855327467996</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B65" t="s">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="C65" t="s">
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="D65" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E65" s="1">
-        <v>0.60293040301773571</v>
+        <v>0.77419354838709675</v>
       </c>
       <c r="F65" s="1">
         <v>22</v>
       </c>
       <c r="G65" s="1">
-        <v>0.61742424016649078</v>
+        <v>0.77272727272727271</v>
       </c>
       <c r="H65" s="1">
-        <v>0.014493837148755099</v>
+        <v>-0.0014662756598240001</v>
       </c>
       <c r="I65" s="1">
-        <v>0.67300812961515244</v>
+        <v>0.9883321736490267</v>
       </c>
       <c r="J65" s="1">
-        <v>0.014493837148755099</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s">
-        <v>27</v>
-      </c>
-      <c r="B66" t="s">
-        <v>73</v>
-      </c>
-      <c r="C66" t="s">
-        <v>150</v>
-      </c>
-      <c r="D66" s="1">
-        <v>91</v>
-      </c>
-      <c r="E66" s="1">
-        <v>0.60293040301773571</v>
-      </c>
-      <c r="F66" s="1">
-        <v>22</v>
-      </c>
-      <c r="G66" s="1">
-        <v>0.61742424016649078</v>
-      </c>
-      <c r="H66" s="1">
-        <v>0.014493837148755099</v>
-      </c>
-      <c r="I66" s="1">
-        <v>0.67300812961515244</v>
-      </c>
-      <c r="J66" s="1">
-        <v>0.014493837148755099</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s">
-        <v>28</v>
-      </c>
-      <c r="B67" t="s">
-        <v>78</v>
-      </c>
-      <c r="C67" t="s">
-        <v>155</v>
-      </c>
-      <c r="D67" s="1">
-        <v>91</v>
-      </c>
-      <c r="E67" s="1">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="F67" s="1">
-        <v>22</v>
-      </c>
-      <c r="G67" s="1">
-        <v>0.090909090909090898</v>
-      </c>
-      <c r="H67" s="1">
-        <v>0.013986013986014</v>
-      </c>
-      <c r="I67" s="1">
-        <v>0.82973704019732786</v>
-      </c>
-      <c r="J67" s="1">
-        <v>0.013986013986014</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>30</v>
-      </c>
-      <c r="B68" t="s">
-        <v>107</v>
-      </c>
-      <c r="C68" t="s">
-        <v>184</v>
-      </c>
-      <c r="D68" s="1">
-        <v>91</v>
-      </c>
-      <c r="E68" s="1">
-        <v>0.30769230769230771</v>
-      </c>
-      <c r="F68" s="1">
-        <v>22</v>
-      </c>
-      <c r="G68" s="1">
-        <v>0.31818181818181818</v>
-      </c>
-      <c r="H68" s="1">
-        <v>0.0104895104895105</v>
-      </c>
-      <c r="I68" s="1">
-        <v>0.9247696454183334</v>
-      </c>
-      <c r="J68" s="1">
-        <v>0.0104895104895105</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>27</v>
-      </c>
-      <c r="B69" t="s">
-        <v>74</v>
-      </c>
-      <c r="C69" t="s">
-        <v>151</v>
-      </c>
-      <c r="D69" s="1">
-        <v>91</v>
-      </c>
-      <c r="E69" s="1">
-        <v>0.40659340659340659</v>
-      </c>
-      <c r="F69" s="1">
-        <v>21</v>
-      </c>
-      <c r="G69" s="1">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="H69" s="1">
-        <v>0.0100732600732601</v>
-      </c>
-      <c r="I69" s="1">
-        <v>0.86306942797487096</v>
-      </c>
-      <c r="J69" s="1">
-        <v>0.0100732600732601</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>30</v>
-      </c>
-      <c r="B70" t="s">
-        <v>108</v>
-      </c>
-      <c r="C70" t="s">
-        <v>185</v>
-      </c>
-      <c r="D70" s="1">
-        <v>91</v>
-      </c>
-      <c r="E70" s="1">
-        <v>0.78021978021978022</v>
-      </c>
-      <c r="F70" s="1">
-        <v>22</v>
-      </c>
-      <c r="G70" s="1">
-        <v>0.77272727272727271</v>
-      </c>
-      <c r="H70" s="1">
-        <v>-0.0074925074925074999</v>
-      </c>
-      <c r="I70" s="1">
-        <v>0.94010805705080525</v>
-      </c>
-      <c r="J70" s="1">
-        <v>0.0074925074925074999</v>
+        <v>0.0014662756598240001</v>
       </c>
     </row>
   </sheetData>
@@ -8956,19 +8503,19 @@
         <v>11</v>
       </c>
       <c r="C2" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D2" s="1">
-        <v>0.67648416757583618</v>
+        <v>0.67828619480133057</v>
       </c>
       <c r="E2" s="1">
-        <v>0.66870665550231934</v>
+        <v>0.66913729906082153</v>
       </c>
       <c r="F2" s="1">
-        <v>0.61083811521530151</v>
+        <v>0.61174750328063965</v>
       </c>
       <c r="G2" s="1">
-        <v>0.64100223779678345</v>
+        <v>0.64271771907806397</v>
       </c>
     </row>
     <row r="3">
@@ -9014,7 +8561,7 @@
         <v>14</v>
       </c>
       <c r="D1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E1" t="s">
         <v>55</v>
@@ -9026,13 +8573,13 @@
         <v>53</v>
       </c>
       <c r="H1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I1" t="s">
         <v>42</v>
       </c>
       <c r="J1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2">
@@ -9043,28 +8590,28 @@
         <v>11</v>
       </c>
       <c r="C2" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D2" s="1">
-        <v>0.87912088632583618</v>
+        <v>0.88172042369842529</v>
       </c>
       <c r="E2" s="1">
-        <v>0.7443820224719101</v>
+        <v>0.74725274725274726</v>
       </c>
       <c r="F2" s="1">
-        <v>0.69827586206896552</v>
+        <v>0.702247191011236</v>
       </c>
       <c r="G2" s="1">
-        <v>0.59340659340659341</v>
+        <v>0.59408602150537637</v>
       </c>
       <c r="H2" s="1">
-        <v>0.58241758241758246</v>
+        <v>0.58602150537634412</v>
       </c>
       <c r="I2" s="1">
-        <v>0.42897727272727271</v>
+        <v>0.42222222222222222</v>
       </c>
       <c r="J2" s="1">
-        <v>0.71698113207547165</v>
+        <v>0.71818181818181814</v>
       </c>
     </row>
     <row r="3">
@@ -9145,25 +8692,25 @@
         <v>11</v>
       </c>
       <c r="C2" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D2" s="1">
-        <v>0.39706959698226424</v>
+        <v>0.39605734713615909</v>
       </c>
       <c r="E2" s="1">
-        <v>0.47695614868304231</v>
+        <v>0.4754355863457726</v>
       </c>
       <c r="F2" s="1">
-        <v>0.38125416210719515</v>
+        <v>0.38044762162752049</v>
       </c>
       <c r="G2" s="1">
-        <v>0.38489119937786687</v>
+        <v>0.38479049279484695</v>
       </c>
       <c r="H2" s="1">
-        <v>0.30196885535350215</v>
+        <v>0.30040321731439201</v>
       </c>
       <c r="I2" s="1">
-        <v>0.3312933507201436</v>
+        <v>0.33086271856420785</v>
       </c>
     </row>
     <row r="3">
